--- a/cv_analyzer/data/applicants.xlsx
+++ b/cv_analyzer/data/applicants.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA26"/>
+  <dimension ref="A1:BA52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -855,7 +855,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>JOB-724ED5BE</t>
+          <t>JOB-925426C4</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>2026-05-14 14:48:44</t>
+          <t>2026-05-19 14:36:20</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>JOB-724ED5BE</t>
+          <t>JOB-925426C4</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>2026-05-14 14:48:44</t>
+          <t>2026-05-19 14:36:20</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>JOB-724ED5BE</t>
+          <t>JOB-925426C4</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>2026-05-14 14:48:44</t>
+          <t>2026-05-19 14:36:20</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>JOB-724ED5BE</t>
+          <t>JOB-925426C4</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2026-05-14 14:48:44</t>
+          <t>2026-05-19 14:36:20</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2873,24 +2873,40 @@
         <v>88</v>
       </c>
       <c r="AP13" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="AQ13" t="n">
-        <v>92.2</v>
+        <v>78.2</v>
       </c>
       <c r="AR13" t="n">
         <v>100</v>
       </c>
       <c r="AS13" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr"/>
+        <v>78.2</v>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>JOB-492B2F1A</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
       <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="inlineStr"/>
+        <v>38.3</v>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>CV Bank Match</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>2026-05-19 14:32:34</t>
+        </is>
+      </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>dylan machingambi pomona city harare machingambid33 gmail.com dob gender male www.linkedin.com/in/dydxa professional summary information technology graduate solid academic foundation one hands-on industrial attachment possesses practical exposure hardware installation troubleshooting network setup end-user support across multiple locations software configuration systems maintenance asset register inventory tracking currently advancing networking expertise through cisco ccna studies ccna1 completed working knowledge tcp/ip fundamentals subnetting routing concepts eager apply proactive solution-oriented mindset technical educational national diploma polytechnic dec certified associate ongoing successfully introduction networks pursuing ccna2 switching wireless essentials certificate moleli high school o-level trainee university zimbabwe january december infrastructure performed configured switches access points waps conducted regular assessments assisted new departmental preventative reporting identify potential vulnerabilities proactively prepared documentation system performance incidents ensure transparency accountability management executed updating operating ensuring compliance security policies hardware/software compatibility tested verified equipment maintained company accurate all operations provided dedicated user emhare platform managed printing services delivered on-site assistance corporate events functions.key strengths protocols dns dhcp vpn firewall awareness switch/wap monitoring diagnostic utilities familiar windows computer repair updates daily problem-solving other microsoft suite mysql class driver license certifications development ccna2references mrs zvigadza manager ict mudondo head department hillary larry giwa coworker sql switch</t>
@@ -3054,24 +3070,40 @@
         <v>76</v>
       </c>
       <c r="AP14" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="AQ14" t="n">
-        <v>84.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AR14" t="n">
         <v>100</v>
       </c>
       <c r="AS14" t="n">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="inlineStr"/>
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>JOB-492B2F1A</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
       <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="inlineStr"/>
+        <v>44.8</v>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>CV Bank Match</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>2026-05-19 14:32:34</t>
+        </is>
+      </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>keith tatenda mugwaziwendota telecommunications graduate engineer location katomba close logan park hatfield harare zimbabwe phone email mugwaziwendotakt gmail.com portfolio https keithmugwaziwendota.vercel.app professional summary engineering hands-on network infrastructure internet things iot artificial intelligence embedded systems expert networking active directory management driven python-driven automation proven track record maintaining uptime delivering complex technical projects ahead schedule security cisco packet tracer sophos/cisco routers switches windows linux firewall configuration tcp/ip lan/wan dns robotics arduino ide raspberry esp32 proteus circuit design simulation pcb programming python html css javascript tools easy eda visual studio code advanced system ads microsoft dynamics/business central hardware specialist aeroclock technicals jan june product reliability engineered tested designs simulations achieving operational client deployments rapid prototyping streamlined design-to-fabrication pipeline reducing prototype iteration time ensuring pre-fabrication accuracy junior attachee national oil company noic aug july optimisation managed sophos environments sustain critical corporate operations expansion successfully deployed lan new depot expanding capacity users cybersecurity secured organisational data managing user permissions implementing rigorous policies support resolved over incidents weekly via automated ticketing average staff downtime improving diagnostic workflows surveillance monitored maintained cctv continuous coverage integrity academic ai-powered wearable assistive designed device computer vision assist visually impaired individuals real-time object detection navigation implemented scripts image processing obstacle collision risks health monitoring developed remote patient microcontroller transmit vital signs server bridged gap between sensors cloud logging demonstrating practical application electronic voting uno programmed unit featuring secure input validation tallying logic rectangular insert-feed rectenna ghz fabricated energy harvesting optimising signal conversion efficiency sustainable power solutions education certifications bachelor honours degree</t>
@@ -3231,16 +3263,16 @@
         <v>45</v>
       </c>
       <c r="AP15" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="AQ15" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="AR15" t="n">
         <v>100</v>
       </c>
       <c r="AS15" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
@@ -3420,16 +3452,16 @@
         <v>28</v>
       </c>
       <c r="AP16" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AQ16" t="n">
-        <v>54.2</v>
+        <v>52.2</v>
       </c>
       <c r="AR16" t="n">
         <v>100</v>
       </c>
       <c r="AS16" t="n">
-        <v>54.2</v>
+        <v>52.2</v>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
@@ -3626,7 +3658,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>JOB-724ED5BE</t>
+          <t>JOB-925426C4</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -3639,12 +3671,12 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Active Job</t>
+          <t>CV Bank Match</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>2026-05-14 15:12:20</t>
+          <t>2026-05-19 14:36:20</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -3819,25 +3851,25 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>JOB-724ED5BE</t>
+          <t>JOB-492B2F1A</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="AV18" t="n">
-        <v>25.77</v>
+        <v>38.3</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Active Job</t>
+          <t>CV Bank Match</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>2026-05-14 15:12:22</t>
+          <t>2026-05-19 14:32:34</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -4012,7 +4044,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>JOB-724ED5BE</t>
+          <t>JOB-925426C4</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -4021,16 +4053,16 @@
         </is>
       </c>
       <c r="AV19" t="n">
-        <v>45.19</v>
+        <v>44.62</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Active Job</t>
+          <t>CV Bank Match</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>2026-05-14 15:12:24</t>
+          <t>2026-05-19 14:36:20</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -4209,7 +4241,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>JOB-724ED5BE</t>
+          <t>JOB-925426C4</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -4218,16 +4250,16 @@
         </is>
       </c>
       <c r="AV20" t="n">
-        <v>39.42</v>
+        <v>38.27</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Active Job</t>
+          <t>CV Bank Match</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>2026-05-14 15:12:26</t>
+          <t>2026-05-19 14:36:20</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -4389,16 +4421,16 @@
         <v>12</v>
       </c>
       <c r="AP21" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="AQ21" t="n">
-        <v>47.8</v>
+        <v>51.2</v>
       </c>
       <c r="AR21" t="n">
         <v>100</v>
       </c>
       <c r="AS21" t="n">
-        <v>47.8</v>
+        <v>51.2</v>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
@@ -4599,7 +4631,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>JOB-724ED5BE</t>
+          <t>JOB-925426C4</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -4612,12 +4644,12 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Active Job</t>
+          <t>CV Bank Match</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>2026-05-14 15:12:30</t>
+          <t>2026-05-19 14:36:20</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -4779,16 +4811,16 @@
         <v>12</v>
       </c>
       <c r="AP23" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="AQ23" t="n">
-        <v>35.8</v>
+        <v>49.8</v>
       </c>
       <c r="AR23" t="n">
         <v>100</v>
       </c>
       <c r="AS23" t="n">
-        <v>35.8</v>
+        <v>49.8</v>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
@@ -4985,25 +5017,25 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>JOB-724ED5BE</t>
+          <t>JOB-CEC891D2</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Hardware Engineer</t>
         </is>
       </c>
       <c r="AV24" t="n">
-        <v>24.62</v>
+        <v>35.39</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Active Job</t>
+          <t>CV Bank Match</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>2026-05-14 15:12:33</t>
+          <t>2026-05-19 11:29:15</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -5165,16 +5197,16 @@
         <v>12</v>
       </c>
       <c r="AP25" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="AQ25" t="n">
-        <v>47.8</v>
+        <v>61.8</v>
       </c>
       <c r="AR25" t="n">
         <v>100</v>
       </c>
       <c r="AS25" t="n">
-        <v>47.8</v>
+        <v>61.8</v>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
@@ -5375,40 +5407,5134 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>JOB-CEC891D2</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>Hardware Engineer</t>
+        </is>
+      </c>
+      <c r="AV26" t="n">
+        <v>41.72</v>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>CV Bank Match</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>2026-05-19 11:29:15</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>spencer jaka harare zimbabwe spencerjaka gmail.com security support trainee professional summary graduate electronic engineer months hands-on bsc hons computer science resolved daily hardware/software tickets gmb cutting downtime while assisting sap inventory/procurement microsoft user issues across windows environments motivated join zhd consulting train services administering learning cctv commissioning leveraging strong troubleshooting customer service networking fundamentals technical/hard outlook teams onedrive python sql tableau power basic tcp/ip domain expertise helpdesk operations incident triage sdlc exposure data analysis reporting soft communication problem solving collaboration time management attention detail technician grain marketing board nov aug reducing end-user improving productivity assisted inventory procurement systems coordinating escalations maintaining continuity stock order processes supported access email file sync during ticket queues ensuring uninterrupted business units education bachelor university degree class certifications google analytics certificate google/coursera automation introduction cybersecurity cisco academy references rupere head dept academic referee trupere ceic.uz.ac.zw masvanhise administrator masvanhisem gmbdura.co.zw hardware</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>2026-05-14 15:12:35</t>
+        </is>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>CVs_2_resume-924318844.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>APP-E4D00E0A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>sibanaevelyn2528@gmail.com</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Evelyn</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Sibanda</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>sibanaevelyn2528@gmail.com</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>+263) 77856634</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>•Diploma in Mental Health</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Diploma/Certificate</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>4</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Evelyn Sibanda - Computer Engineer | IT Support &amp; Customer</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>ASIC, Business, C, CD, CI, Communication, ERP, ESP32, Electronics, Embedded, Embedded Systems, Git, GitHub, Hardware, IPS, IT Support, IoT, Machine Learning, Marketing, Microcontroller, Mobile, Monitoring, Networking, Performance, RF, SAP, Sales, Security, Testing, Windows</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>45</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>49</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>49</v>
+      </c>
+      <c r="AT27" t="inlineStr">
+        <is>
+          <t>JOB-925426C4</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="AV27" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>CV Bank Match</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>2026-05-19 14:36:20</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>evelyn sibanda computer engineer support customer service professional nationality zimbabwean gender female phone number mobile email address sibanaevelyn2528 gmail.com website www.linkedin.com/in/evelyn-sibanda-63b420292 zimbabwe home results-driven engineering graduate strong foundation embedded systems networking fundamentals electronic integration experienced hardware troubleshooting customer-facing technical digital operational coordination within multicultural environments skilled diagnosing issues supporting infrastructure collaborating teams improve delivery system efficiency recognized communication adaptability professionalism willingness learn emerging technologies passionate applying problem-solving real-world security projects smart safety final project grade designed developed iot-based esp32 microcontroller technology real-time environmental monitoring detection integrated calibrated multiple sensors including gas air quality temperature humidity motion flame ensure accurate performance implemented wi-fi connectivity web server lcd display rgb led alerts automated buzzer notifications arduino ide applied iot principles throughout development testing among best stream linkhttps github.com/profevelyn/ mis intern starcore electronics guzelyurt cyprus diagnosed optimized while operations assisted software installations inventory management organization collaborated gained exposure business sales client relations marketing assistant baobab real estate kwekwe managed front desk inquiries property consultations maintaining engagement supported through whatsapp promotions social media advertising lead follow-ups relationship coordinated viewings maintained records between clients agents representative megasound company delivered during events resolved concerns effectively smooth built relationships vice president miss africa north manc nicosia guest hosting attendees ensured guests felt welcomed informed comfortable represented professionally public cultural engagements worked under high pressure situations production worker trodos lefke followed standards organized clean workstations outstanding employee till operator mega trade handled high-volume transactions accurately volunteer mental health advocate counselor diploma provided emotional active listening respectful confidential manner</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>2026-05-19 10:57:01</t>
+        </is>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>cVS_4_resume-208553773.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>APP-635177A6</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>tsitsi.munyaradzi@gmail.com</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TSITSI</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>MUNYARADZI</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>tsitsi.munyaradzi@gmail.com</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>+263 71 012 3456</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Address: 14 Waterfalls Avenue</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Nationality: Zimbabwean; Address: 14 Waterfalls Avenue, Waterfalls, Harare, Zimbabwe; Bachelor of Science Honours Degree in Electronic Engineering – University of Zimbabwe (2022 to 2026); Certificate in Hardware Testing and Verification (LinkedIn Learning, 2024); 1. Hardware QA Intern – Emerson Electric Zimbabwe (June 2024 – September 2024); 2. Electronics Club Chairperson – University of Zimbabwe Electronics Society (2023 – 2024); Organisation: University of Zimbabwe; Organisation: Emerson Electric Zimbabwe</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>23</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Hardware Engineering Student</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>C, CI, Electronics, Embedded, Hardware, Machine Learning, Mobile, PCB, Python, REST, RF, Testing</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>88</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>47</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="AT28" t="inlineStr">
+        <is>
           <t>JOB-724ED5BE</t>
         </is>
       </c>
-      <c r="AU26" t="inlineStr">
+      <c r="AU28" t="inlineStr">
         <is>
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="AV26" t="n">
-        <v>22.31</v>
-      </c>
-      <c r="AW26" t="inlineStr">
+      <c r="AV28" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="AW28" t="inlineStr">
         <is>
           <t>Active Job</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>2026-05-14 15:12:35</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>spencer jaka harare zimbabwe spencerjaka gmail.com security support trainee professional summary graduate electronic engineer months hands-on bsc hons computer science resolved daily hardware/software tickets gmb cutting downtime while assisting sap inventory/procurement microsoft user issues across windows environments motivated join zhd consulting train services administering learning cctv commissioning leveraging strong troubleshooting customer service networking fundamentals technical/hard outlook teams onedrive python sql tableau power basic tcp/ip domain expertise helpdesk operations incident triage sdlc exposure data analysis reporting soft communication problem solving collaboration time management attention detail technician grain marketing board nov aug reducing end-user improving productivity assisted inventory procurement systems coordinating escalations maintaining continuity stock order processes supported access email file sync during ticket queues ensuring uninterrupted business units education bachelor university degree class certifications google analytics certificate google/coursera automation introduction cybersecurity cisco academy references rupere head dept academic referee trupere ceic.uz.ac.zw masvanhise administrator masvanhisem gmbdura.co.zw hardware</t>
-        </is>
-      </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>2026-05-14 15:12:35</t>
-        </is>
-      </c>
-      <c r="BA26" t="inlineStr">
-        <is>
-          <t>CVs_2_resume-924318844.pdf</t>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>2026-05-19 10:57:07</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>tsitsi munyaradzi hardware engineering student personal details name d.o.b october sex female marital status single nationality zimbabwean contact address waterfalls avenue harare zimbabwe mobile email tsitsi.munyaradzi gmail.com linkedin summary enthusiastic disciplined keen interest consumer electronics design embedded testing hardware-software co-design detail-oriented creative committed producing high-quality enjoy working multidisciplinary teams always eager learn new tools methodologies academic professional bachelor science honours degree electronic university certificate verification learning introduction udemy advanced level dominic high school chishawasha mathematics physics computer points ordinary ten passes projects bluetooth speaker designed assembled portable including class amplifier circuit lithium battery charging printed enclosure usb power bank charger tp4056 protection mosfets boost converter output stage hardware-in-the-loop hil test rig built validating controller outputs against simulated responses control systems lab intern emerson electric june september conducted pcb inspection boundary scan functional equipment documented results non-conformances quality management system assisted developing procedures product lines club chairperson society organised workshops competitions guest lectures students managed budget usd project materials events abilities prototyping proficient kicad schematic capture layout oscilloscopes dmms curve tracers familiar ipc-a-610 standards acceptability audio topologies li-ion li-po circuits python scripting automated reporting strong attention detail assurance mindset career objective join organisation where contribute validation while building practical industry referees eng chieza lecturer phone gchieza eng.uz.ac.zw mutero lead amutero emerson.com machine rest</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>2026-05-19 10:57:07</t>
+        </is>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>cVS_4_resume-353977502.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>APP-A8528E07</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>farai.mutenha@gmail.com</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>FARAI</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>MUTENHA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>farai.mutenha@gmail.com</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>+263 78 901 2345</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Address: 9 Marlborough Close</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Nationality: Zimbabwean; Address: 9 Marlborough Close, Marlborough, Harare, Zimbabwe; Bachelor of Engineering Honours Degree in Electrical Power Engineering – Harare Institute of Technology (2021 to 2025); Certificate in Power Electronics Design (Coursera – University of Colorado, 2024); 2. Eng. S. Chiramba (Technical Director); Email: schiramba@nyangani.co.zw</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>22</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Hardware Engineering Student</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>AutoCAD, Business, C, CI, Electronics, Hardware, Machine Learning, Mobile, PIC, SPI, Switch, Testing</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>88</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="AT29" t="inlineStr">
+        <is>
+          <t>JOB-724ED5BE</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="AV29" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Active Job</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>2026-05-19 10:57:09</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>farai mutenha hardware engineering student personal details name d.o.b january sex male marital status single nationality zimbabwean contact address marlborough close harare zimbabwe mobile email farai.mutenha gmail.com linkedin summary confident technically adept expertise power electronics renewable energy systems high-voltage circuit design bring results-driven mindset hands-on conversion keen apply environment focused sustainable solutions academic professional bachelor honours degree electrical institute technology certificate coursera university colorado grid-connected zera accredited advanced level prince edward school mathematics physics chemistry points ordinary twelve passes projects dc-dc boost converter designed built mosfet switching pwm control achieving over efficiency off-grid solar applications single-phase grid-tie inverter simulated grid-tied matlab/simulink gate driver h-bridge configuration battery management system bms li-ion cell balancing overcurrent protection state-of-charge indicator dedicated bq76920 intern nyangani june december assisted reviews site inspections small hydro generation supported procurement testing inverters charge controllers installations prepared load analysis reports single-line diagrams customer sites assistant contractors family business installed commissioned residential commercial wiring board earthing lighting setups abilities converters rectifiers regulators simulation loop mosfet/igbt pspice ltspice familiar iec standards storage thermal enclosures autocad schematic drawing panel career objective obtain industrial attachment where contribute commissioning deepen referees mhizha lecturer organisation phone emhizha hit.ac.zw eng chiramba technical director schiramba nyangani.co.zw machine learning pic spi switch</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>2026-05-19 10:57:09</t>
+        </is>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>cVS_4_resume-358949493.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>APP-AAC6517D</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ellenchipezeze@gmail.com</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ELLEN</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CHIPEZEZE</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ellenchipezeze@gmail.com</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>+263788882845</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>• Midlands State University : BCom Honours Degree in in Information Systems (Class 2.1); • Mabvuku High School : Advanced Level Certificate; • Queen Elizabeth Girls High : Ordinary Level Certificate : 8 subjects Incl Mathematics and English</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Degree</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>21</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>faults, vulnerabilities, and security concerns to senior system administrators.</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>ASIC, Azure, Backup, C, CI, CSS, Cloud, Communication, Data Analysis, Excel, HTML, Hardware, Helpdesk, IT Support, Java, JavaScript, Less, Machine Learning, Microsoft Azure, Monitoring, MySQL, Networking, Oracle, Performance, RF, Router, SPI, SQL, Security, Switch, TCP/IP, Windows</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>88</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AT30" t="inlineStr">
+        <is>
+          <t>JOB-492B2F1A</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="AV30" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>CV Bank Match</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>2026-05-19 14:32:34</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>ellen chipezeze eastlea harare ellenchipezeze gmail.com d.o.b professional summary experienced support systems administrator skilled hardware software troubleshooting system deployment end-user across retail healthcare environments proven translate complex technical issues user-friendly solutions ensuring efficient service delivery minimal downtime operating windows installation configuration diagnostics repairs preventive maintenance helpdesk networking tcp/ip network lan setup router switch cloud identity microsoft azure fundamentals active web development basic front-end html css javascript tools office suite utilities updates database data management mysql sql queries excel analysis other collaboration communication problem-solving time assistant tech360.zw nov april diagnosed resolved including slowdowns boot failures peripheral connectivity problems users installed configured maintained applications performance optimization workstations provided end during laptops desktop computers fully functional user-ready peripherals such printers scanners external storage devices seamless integration existing performed upgrades ram replacement improving efficiency longevity troubleshot networks router/switch configurations over devices/users intern parirenyatwa group hospitals jan aug monitored hospital infrastructure proactively identifying escalating faults vulnerabilities security concerns senior administrators assisted maintaining uptime supporting routine checks servers networked scheduled backups integrity availability supported recovery operations case loss incidents activities physical cabling address collaborated staff resolve reducing reliability documented resolutions standard procedures contributing improved knowledge sharing faster problem resolution within managing inventory tracking assets monitoring license usage ensure compliance education midlands state university bcom honours degree information class mabvuku high school advanced level certificate queen elizabeth girls ordinary subjects incl mathematics english certificates training oracle artificial intelligence asic backup java less machine learning spi</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>2026-05-19 10:57:17</t>
+        </is>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>cVS_4_resume-650793540.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>APP-AF704A9A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>filtersubscribers:721431</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Subscribers</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>080 07721431</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Subscriber; Filter Subscribers; 1 Selected Subscriber(s); Subscriber Product; Add Subscriber</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Degree</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>C, LTE, Less, Machine Learning, Mobile</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="AT31" t="inlineStr">
+        <is>
+          <t>JOB-724ED5BE</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="AV31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Active Job</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>2026-05-19 10:57:20</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>subscriber management filter subscribers data recharges show rows start selected product name phone number code status airtime dvmu13 pedzi usd recharge log netone econet private wifi voice confirm zesa token telone products nyaradzo payment bulk view transactions sold pins delete add system currently online mobile brand blessing active zhakata ice econet078 nyasha mavedzenge quedrue zhd lte less machine learning</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>2026-05-19 10:57:20</t>
+        </is>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>cVS_4_resume-660923825.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>APP-06F5064F</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>makoniprevilledgepaidamoyo@gmail.com</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PREVILLEDGE</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>PAIDAMOYO</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>makoniprevilledgepaidamoyo@gmail.com</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>+263783 932 549</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>71 Lowli Avenue</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>• National Diploma in Information Technology, Gweru Polytechnic</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Diploma/Certificate</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>22</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Programming in C++ Hardware Technician Data Entry</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>C, C++, CI, Communication, DBA, ERP, Go, Hardware, Machine Learning, Performance, RF</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>88</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="AT32" t="inlineStr">
+        <is>
+          <t>JOB-724ED5BE</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="AV32" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Active Job</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>2026-05-19 10:57:23</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>previlledge paidamoyo makoni lowli avenue belvedere harare zimbabwe telephone email makoniprevilledgepaidamoyo gmail.com objectives seeking suitable appropriate career organization commensurate academic professional part dynamic world only utilize present skill also promote acquisition development new core competencies provide feedback computer performance impart necessary knowledge staff under pressure minimum supervision self-motivated sense self driven achievement good communication interpersonal highly organized innovative resourceful personal details date birth february sex female national i.d s-27 nationality zimbabwean languages spoken english shona religion christian education january december ordinary level passes progress college advanced mkoba high school april certificate information technology gweru polytechnic august diploma programming hardware technician data entry network administration configuration technical support magistrates court main street itayimhlanga references manager gwaze head department mhlanga dba erp machine learning</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>2026-05-19 10:57:23</t>
+        </is>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>cVS_4_resume-755575558.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>APP-3D5540D9</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>princemukuvisi</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PRINCE</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>MUKUVISI</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>SOFTWARE ENGINEER</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AT33" t="inlineStr">
+        <is>
+          <t>JOB-724ED5BE</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="AV33" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Active Job</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>2026-05-19 10:57:24</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>prince mukuvisi software engineer</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>2026-05-19 10:57:24</t>
+        </is>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>cVS_4_resume-798516372.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>APP-A1223502</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>enock.xik@gmail.com</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ENOCK</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CHIKANDA</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>enock.xik@gmail.com</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0786079619</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>29/08/2001</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>24</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Shona</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Technical Software tools and Certificates; Network Troubleshooting (TCP/IP, Diploma In; Assisted in the support and maintenance of STMS (Zimbabwe Republic Police) systems, providing</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>25</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>An electronic support engineer proffesional with strong problem-solving skills and hands-on experience</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>C, CI, CSS, Communication, ERP, Go, HTML, Hardware, Java, JavaScript, Less, Machine Learning, Monitoring, Performance, PostgreSQL, Python, RF, Router, SQL, TCP/IP, Windows, Wireless</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>88</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="AT34" t="inlineStr">
+        <is>
+          <t>JOB-925426C4</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="AV34" t="n">
+        <v>43.46</v>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>CV Bank Match</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>2026-05-19 14:36:20</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>enock chikanda gender male email enock.xik gmail.com call dob address budiriro harare languages ndebele shona english electronic support engineer proffesional strong problem-solving hands-on diagnosing resolving network hardware software issues skilled supporting ict systems routers wireless infrastructure while ensuring reliable connectivity minimal downtime committed delivering efficient customer-focused maintaining high service standards technical tools certificates technologies troubleshooting tcp/ip diploma javascript html css engineering wifi aps hotspot python telone center system installation configuration java learning maintenance postgres sql windows environment microsoft office documentation reporting class drivers ticketing incident logging customer communication licence professional expirience pvt intern provided day-to-day enterprise applications responding incidents requests ensure availability user satisfaction supported production including sms gateway stable operations monitoring timely resolution faults assisted stms zimbabwe republic police providing application-level data validation operational delivered insureme assisting users functionality backend-related smart solutions robert mugabe international airport ongoing high-availability documented resolutions procedures contributing knowledge base guides worked closely development teams resolve escalated clear user-friendly non-technical effective issue guidance personal project designed implemented community configuring access points provide controlled internet manage bandwidth allocation performance referencies willard mhaka fidelis gwokuda sedrick manyiwa product manager developer willard.mhaka telone.co.zw fidelis.gwokuda sedrick.nyanyiwa erp less machine postgresql router</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>2026-05-19 11:20:51</t>
+        </is>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>Cvs_5_resume-21905465.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>APP-472C463A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ashleymnakandafa@gmail.com</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ASHLEY</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>MNAKANDAFA</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ashleymnakandafa@gmail.com</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0772959779</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Mutare</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>BScHonoursinComputerSystemsEngineering—MidlandsStateUniversityGraduatedSeptember2025</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Degree</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>18</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>ComputerSystemsEngineer|EmbeddedSystems&amp;IoT|Networking</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>ASIC, Business, C, C++, CD, CI, Cisco, Cloud, DBA, Deno, EDA, Embedded, Firewall, GSM, Git, Go, Hardware, I2C, IoT, Java, LTE, Machine Learning, Monitoring, MySQL, Networking, NumPy, Pandas, Performance, PostgreSQL, Python, REST, RF, Router, SQL, Sales, Sass, Security, Switch, TensorFlow, UDP, VPN</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>76</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="AT35" t="inlineStr">
+        <is>
+          <t>JOB-724ED5BE</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="AV35" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Active Job</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>2026-05-19 11:21:13</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>ashley mnakandafa computersystemsengineer embeddedsystems iot networking mutare zimbabwe opentorelocation ashleymnakandafa gmail.com linkedin driver slicense class4 career objective results-drivencomputersystemsengineeringgraduatewithhands-onexperienceinembeddedsystems andmachinelearningdeployment.provenabilitytodesignandbuildreal-worldsolutions anadasprototypeonraspberrypi5togsm-basedindustrialmonitoringsystems.bringacreative analytical mindset strong eagerness learn approach problems fresh perspectives seekinganitrolewhereicanapplymytechnicalfoundationandgrowwithinadynamicteam education bschonoursincomputersystemsengineering midlandsstateuniversitygraduatedseptember2025 class2.1 strongperformanceacrossembeddedsystems andsoftwareengineering modules certifications ciscoskillsforall introductiontoiot introductiontodatascience introductiontocybersecurity cyberthreatmanagement ethicalhacker hexcocertificate itfield itintern industrialattachment highcourtofzimbabwe august2023 august2024 itofficerduties configured installedandmaintainednetworkhardwareincludingswitches routersandaccesspointsfor a100+userenvironment provideddailyitsupport resolvinghardwarefaults black-screenissues softwarecrashesand connectivityproblemsacrosscourtmachines monitorednetworkperformanceusingwireshark solarwindsandunificontroller diagnosedand resolvedconnectivityissues supported2 ensuringstableavandnetwork connectivity performednetworkcabling portlabeling ipaddressmanagementanddocumentationupdates assistedinconfiguringfirewalls vpnsandbasicnetworksecuritypoliciesundersupervision e-filingofficerduties voluntary guidedlawyersandmembersofthepublicthroughcreatingiecmsaccountsandfilingcourtcases digitally providedfrontlineassistanceatthee-filingdesk improvingdigitaladoptionandreducingfilingerrors receptionist managedfront-deskoperationsincludingvisitorcoordination callroutingandadministrativesupport salesassistant informalittechnician retailshop october2025 present diagnoseandrepairsmarttvs smartphonesandpersonalcomputersforcustomersandwalk-inclients resolvehomeandsmallbusinessnetworkconnectivityissuesincludingrouterconfigurationandwi-fi troubleshooting performsoftwareinstallations osupdates antivirussetupandgeneraldevicemaintenance handlesalesoperationswhiledoublingasthego-totechnicalresourceforthebusiness academic technical projects adasprototype raspberrypi5 finalyearproject designedanddevelopedamulti-functionaladvanceddriverassistancesystemwithobjectdetection lanedetectionandreal-timesafetyalerts deployedatrainedmlpmodel tflite forultrasonic-basedobjectclassification pedestrian car motorbike bus anda1dcnnforsignaldenoising implementedspeed-adaptiveforwardcollisionwarning fcw andblind-spotdetection bsd logicwith apriorityalerthierarchy lane engine builtenginethermalriskmonitoringusingdht11sensordataandamachinelearningpredictionmodel integrated16x2lcddisplay buzzeralerts ledindicatorsandbluetoothmotorcontrolforafulldriver feedbackinterface technologies python tensorflowlite arduinomega ultrasonicsensors irsensors dht11 gsm-basedindustrialfaultmonitoringsystem academicproject builtaniotmonitoringsystemthatdetectsgas/smoke abnormaltemperatureandunauthorizedmotion inindustrialenvironments systemsendsautomatedsmsalertstodesignatedpersonnelinrealtimeuponfaultdetection integratedpirmotionsensor mq-seriessmokesensoranddht11temperaturesensorwithanarduino andsim900lgsmmodule displayedlivesensorreadingsona16x2lcdwiththreshold-basedalertinglogic arduino sim900lgsm pirsensor liquidcrystali2c programminglanguages c/c primary java beginner embedded raspberry mega gpio ultrasonic/ir/dht11 sensors sim900l gsm l298nmotordriver machinelearning mlp modeltraining edgedeployment pandas numpy networkingtools gns3 ciscopackettracer solarwinds unificontroller wireshark putty databases postgresql mysql firebase sqlserver developertools git vscode jetbrainsides kaggle googlecloudplatform basic languages english fluent shona french interests roboticsandautomotivesafetytechnology datascienceandmachinelearningforreal-worldapplications chess analyticalthinkingandstrategicproblem-solving keepingupwithemergingtechnologytrends references availableonrequest orcontactbelow tafadzwadyirakumunda highcourtsheriff tawandamlambo itofficer mlambotawanda mr.g.r.mushati principalitofficer manicaland gmushati jsc.org.zw asic business cisco cloud dba deno eda firewall hardware i2c lte machine learning monitoring performance rest router sql sales sass security switch tensorflow udp vpn</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>2026-05-19 11:21:13</t>
+        </is>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>Cvs_5_resume-321185774.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>APP-D04AD17D</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>emmanuelchingwena@live.com</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMMANUEL</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ANESU</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>emmanuelchingwena@live.com</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>+263 71 329 8071</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Bindura</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>BSc (Hons) in Computer Science – Upper Second Class (2.1)</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Degree</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>2</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>augmented generation (RAG) and prompt engineering. Reliable, adaptable, and solution-oriented</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>C, CI, ERP, Git, Hardware, IT Support, Linux, Machine Learning, Monitoring, Networking, Next.js, Outlook, Performance, REST, RF, SQL, ServiceNow, TCP/IP, Windows</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="AT36" t="inlineStr">
+        <is>
+          <t>JOB-492B2F1A</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="AV36" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>CV Bank Match</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>2026-05-19 14:32:34</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>emmanuel anesu chingwena bindura zimbabwe emmanuelchingwena live.com emmanuel.chingwena outlook.com linkedin linkedin.com/in/emmanuel-anesu-chingwena professional profile computer science graduate bsc honours upper second class hands-on support systems administration enterprise technology environments skilled technical troubleshooting system configuration sql databases modern web technologies including next.js experienced network infrastructure tcp/ip dns dhcp service management tools such servicenow developed ai-powered intelligent tutoring retrieval augmented generation rag prompt engineering reliable adaptable solution-oriented strong foundation both administrative computing disciplines first-line second-line windows linux microsoft installation deployment networking lan wan fundamentals performance monitoring development database design framework retrieval-augmented git version control virtualization vmware virtualbox intern bancabc head office harare september october provided end-users resolving hardware software connectivity issues assisted maintaining supported updates patch deployments documented procedures steps user guides assistant weighbridge clerk fsg superfert accurately captured logistics weight data operational records prepared detailed reports record-keeping processes projects featuring automated quiz generator chatbot implemented contextual response question techniques integrated storage learning content education hons university buse levels biology chemistry pure mathematics passes english language chipadze high school additional information nationality zimbabwean languages fluent shona native interests hobbies graphic creating promotional flyers cards digital media drawing chess board games socialising references muzembe senior manager amuzembe bancabc.co.zw bhunu administrator tamuka.bhunu fsg.co.zw chaka chairperson department pchaka buse.ac.zw erp machine outlook rest</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>2026-05-19 11:21:16</t>
+        </is>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>Cvs_5_resume-478705439.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>APP-6B7F0272</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>opulentmagomo@gmail.com</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>OPULENT</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CHIKWIRAMAKOMO</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>opulentmagomo@gmail.com</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>077 725 6044</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Bachelor of Commerce (Honours) Degree in Data Science and Informatics</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Degree</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>C, CI, Communication, Data Analysis, Data Science, ERP, Git, Go, Hardware, IT Support, Machine Learning, Networking, Performance, Python, REST, RF, Security, VoIP</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>100</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AT37" t="inlineStr">
+        <is>
+          <t>JOB-724ED5BE</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="AV37" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Active Job</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>2026-05-19 11:21:22</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>opulent chikwiramakomo chitungwiza zimbabwe opulentmagomo gmail.com career objective data science graduate hands-on internship support troubleshooting networking database management passionate technology infrastructure emerging digital solutions strong willingness learn grow enterprise electronic security environments education bachelor commerce honours degree informatics midlands state university upper second class technical cid fundamentals microsoft python analysis hardware systems maintenance cybersecurity awareness professional customer service intern wozatel online aug provided communication assisted maintaining voip e-learning platforms monitored system performance resolved issues collaborated teams improve delivery forestry commission jan maintained optimized databases organizational operations supported integration migration processes system-related ensured accuracy accessibility reporting project energy consumption anomaly detection developed machine learning models identify abnormal usage patterns applied techniques preprocessing visualized insights through dashboards analytical reports soft problem-solving effective collaboration adaptability continuous additional information driver licence erp git rest</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>2026-05-19 11:21:22</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>Cvs_5_resume-52415892.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>APP-BAED8867</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ira@outlook.com</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>RUKUDZO</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NATALIE</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ira@outlook.com</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>263774343311</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Windows Server</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>• National Diploma in Information Technology, Bulawayo Polytechnic | 2025; • National Certificate in Information Technology, Bulawayo Polytechnic | 2022</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Diploma/Certificate</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>24</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Cephas Fumhanda | Information Technology Manager | Mpilo Central Hospital, Bulawayo</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>ASIC, Backup, Business, C, C++, CI, CSS, Desktop Support, Excel, Firewall, Git, HTML, Hardware, Helpdesk, IPS, IT Support, Java, JavaScript, Less, Machine Learning, Monitoring, MySQL, Outlook, PHP, Power BI, REST, Restore, Router, SPI, SQL, Security, Switch, Windows, Wireless, Word</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>1</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>88</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="AT38" t="inlineStr">
+        <is>
+          <t>JOB-492B2F1A</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="AV38" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>CV Bank Match</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>2026-05-19 14:32:34</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>rukudzo natalie mutswakatira information technology graduate rnmutswakatira outlook.com harare driver license class professional profile network infrastructure configuration support help desk computer systems administration skilled configuring firewall security protocols managing windows server environments hardware software troubleshooting repairs restoring critical ensure uninterrupted healthcare delivery value proposition proven track record maintaining switches routers wireless access points hands-on administrating user accounts controls diagnosing resolving operating system faults timely manner experienced helpdesk weekly tickets training high uptime proficient microsoft office suite working knowledge tools applications assisted fortigate audits patch management control enforcement fast learner strong analytical eye identifying anomalies master new technics problem-solving capacity independently collaboratively under deadline pressure competent backups disaster recovery procedures business continuity core maintenance technical service operations digital literacy asset web development php javascript mysql backup execution remote desktop intern mpilo central hospital bulawayo january december contributed hospital-wide point installation achieving coverage across all wards administered staff departments logged tracked resolved data queries operational productivity promptly log deployed configured tested documented workstations printers verifying full functionality supporting lan connectivity interconnected restored non-functional equipment through component-level repair executed daily monitoring maintained accurate ict inventory records education certifications memberships national diploma polytechnic certificate a-level passes science studies geography o-level including mathematics english language proficiency excel word outlook router/switch visual studio code css html basic power epi info application adobe photoshop illustrator referees cephas fumhanda manager cephasfumhanda gmail.com hatina mahosi officer hmahosi beatrice mateza lecturer charge bmateza asic git ips java less machine learning rest restore router spi sql switch</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>2026-05-19 11:21:34</t>
+        </is>
+      </c>
+      <c r="BA38" t="inlineStr">
+        <is>
+          <t>Cvs_5_resume-780856169.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>APP-1C42382B</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>kumbiraimushambi08@gmail.com</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Computer</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>kumbiraimushambi08@gmail.com</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0786280990</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>BSc Computer Hardware Engineering — University of Zimbabwe |AUG 2021 – JUL 2025 | Upper</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>4</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Computer Engineer</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>API, ASIC, Backup, C, CI, CRM, Communication, Django, ERP, Ethernet, Excel, Finance, Flask, Go, Hardware, IPS, Java, JavaScript, Linux, Machine Learning, Monitoring, Networking, Node.js, Performance, Python, REST, RF, React, Restore, Router, SQL, SQL Server, Security, Switch, Testing, Unit Testing, Windows</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>1</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>45</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>61</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>61</v>
+      </c>
+      <c r="AT39" t="inlineStr">
+        <is>
+          <t>JOB-925426C4</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="AV39" t="n">
+        <v>41.15</v>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>CV Bank Match</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>2026-05-19 14:36:20</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>kumbirai mushambi crescent glenview computer engineer kumbiraimushambi08 gmail.com resourceful detail-oriented bsc hardware engineering upper second-class degree strong foundation systems software development support networking proven build manage scalable web applications troubleshoot complex integrate technologies across devices platforms experienced database management erp administration sage contributing policy cybersecurity initiatives education university zimbabwe aug jul second class cambridge a-level bernard mizeki college mathematics physics science chemistry o-level subjects including oct intern cernol chemicals pvt harare maintenance administered windows linux servers diagnosed resolved network faults provided remote users rdp any desk demonstrated sql server schema design performance tuning backups recovery executed daily system maintained operational logs circulated weekly tips all branches user created managed accounts roles internal enforced access controls asset documentation inventories updated application manuals produced runbooks after updates reporting data capture ensured timely branch generated monthly ad-hoc reports submitted required mis head office installed troubleshot lan/wi-fi switches routers endpoints technician contractor netcab tested documented ethernet fiber cabling configured points performed site surveys layout records technical logged incidents per company procedures test device connectivity core python javascript node.js react django flask analysis coding standards unit testing release notes databases integration query writing validation report generation basic api infrastructure basics endpoint configuration restore incident logging resolution virtualization exposure professional clear written verbal communication teamwork stakeholder engagement sops knowledge articles disciplined change participation other anydesk excel troubleshooting aptitude willingness on-call projects crm app full-stack feature delivery backend frontend implemented ticketing role-based guides trained staff real-time patient monitoring arrhythmia detection built edge pipeline deployed inference raspberry relevant</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>2026-05-19 11:21:37</t>
+        </is>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>Cvs_5_resume-824311754.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>APP-5A1B0E9B</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ruvimbo.mhuriro@gmail.com</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>RUVIMBO</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>MHURIRO</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ruvimbo.mhuriro@gmail.com</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>+263 71 678 9012</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Address: 5 Hatfield Road</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Nationality: Zimbabwean; Address: 5 Hatfield Road, Hatfield, Harare, Zimbabwe; A driven and innovative hardware engineering student with a deep interest in telecommunications hardware, signal processing, and RF circuit design. I am a disciplined, methodical individual who applies systematic thinking to complex hardware challenges. I am passionate about contributing to Zimbabwe's telecommunications infrastructure through quality engineering.; Bachelor of Engineering Honours Degree in Telecommunications Engineering – Harare Institute of Technology (2022 to 2026); Certificate in RF and Wireless Communication Fundamentals (Coursera, 2024); 1. Telecommunications Hardware Intern – Liquid Technologies Zimbabwe (June 2024 – September 2024); Led a team that competed in the Zimbabwe Science Fair, winning second place for an electronics project.</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>20</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Hardware Engineering Student</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>C, CI, Communication, EDA, Electronics, Hardware, LTE, Less, Machine Learning, Mobile, PIC, REST, RF, SPI, Signal Processing, Telecom, Testing, Wireless</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>88</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="AT40" t="inlineStr">
+        <is>
+          <t>JOB-925426C4</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="AV40" t="n">
+        <v>38.85</v>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>CV Bank Match</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>2026-05-19 14:36:20</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>ruvimbo mhuriro hardware engineering student personal details name d.o.b may sex female marital status single nationality zimbabwean contact address hatfield road harare zimbabwe mobile email ruvimbo.mhuriro gmail.com linkedin summary driven innovative deep interest telecommunications signal processing circuit design disciplined methodical individual who applies systematic thinking complex challenges passionate contributing infrastructure through quality academic professional bachelor honours degree institute technology certificate wireless communication fundamentals coursera introduction matlab mathworks online advanced level dominican convent high school mathematics physics chemistry points ordinary twelve passes projects radio transmitter designed constructed short-range operating mhz band discrete transistor amplifier stages tank analyser dashboard developed matlab-based visualising fft spectra filtering simulated signals teaching demo lab lte antenna microstrip patch bands ansys hfss simulation software final coursework project intern liquid technologies june september supported configuration testing fibre-optic transmission assisted fault identification resolution wan lan links prepared site survey reports equipment installation documentation science club coordinator organised electronics workshops experiments junior students led competed fair winning second place abilities ltspice proficient matlab/simulink system modelling understanding theory microwave principles familiar spectrum vna vector network operation knowledge modulation techniques ofdm qam line impedance matching competent microsoft office visio latex strong technical report writing career objective pursue industrial attachment within environment applying systems support real-world operations referees muchenje lecturer organisation phone mmuchenje hit.ac.zw eng banda planning engineer lbanda liquid.tech eda less machine learning pic rest spi telecom</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>2026-05-19 11:21:43</t>
+        </is>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>Cvs_5_resume-996365866.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>APP-53B76F55</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>tadiwanashendemera57@gmail.com</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>TADIWANASHE</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>BEAULAH</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>tadiwanashendemera57@gmail.com</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>0780108495</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Degree Class in Information Technology. With my IT background, l am confident in my ability to; BACHELOR OF SCIENCE HONOURS DEGREE IN INFORMATION TECHNOLOGY; GPA:2.8 DEGREE CLASS: B+ (Upper Second Class) (2.1)</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Degree</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>ENGINEER</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Active Directory, Backup, Business, Business Intelligence, C, CI, Cisco, Communication, Excel, Exchange, Go, Hardware, IMS, Machine Learning, Mobile, MySQL, Networking, Oracle, Outlook, Project Management, Router, SQL, Security, Windows, Word</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="AT41" t="inlineStr">
+        <is>
+          <t>JOB-925426C4</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="AV41" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Active Job</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:32:14</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>tadiwanashe beaulah ndemera email tadiwanashendemera57 gmail.com address sunningdale harare dear recruitment application graduate trainee electronic security support engineer regards above matter excited apply aas advertised chinhoyi university science technology holding upper second degree class information background confident contribute success leverage technical knowledge dynamic environment like yours during month attachment telecel zimbabwe gained valuable including network management configured cisco routers troubleshooting connectivity issues installing anti-viruses updates backups generated solar-wind reports active directory managed user accounts resetting passwords granting access rights permissions microsoft exchange server created mailboxes manage databases well e.g login mail flow office365 resolved outlook word excel virtual machine vms vmware workstation hyper-v box users machines thus building new windows billing project would ensure projects completed time meeting deadlines business intelligence mobile financial services jobs individual capable working minimal supervision eager learn more towards career path enclosed please find copy which provides additional academic review thank consideration looking forward response sincerely bachelor honours institution gpa other educational ordinary level passes mathematics english zimsec advanced networking configuring solar winds operating systems macos database mysql oracle sql developer hardware software updating drivers setting printers computers joining domain applications asset register itequipment laptops allocation remote tools any desk desktop connection teamviewer soft problem solving teamwork good communication valid driver license references mrs mutirikwi roaming leader masamha lecturer-ict department backup ims learning router</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:32:14</t>
+        </is>
+      </c>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>Cvs_7_resume-112171568.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>APP-5D5E1DB2</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>marambis@staff.msu.ac.zw</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Mr</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Kudzinyadza</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>marambis@staff.msu.ac.zw</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>+263 77 319 2974</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Avenue</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Master of Commerce Degree in Information Systems Expected July 2027</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>2</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Freelance IT Support &amp; Systems Developer</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>API, ASIC, Accounting, Active Directory, Business, C, CI, CRM, Cisco, Cloud, Communication, Data Analysis, Git, GitHub, Go, Hardware, IT Support, Java, Less, Machine Learning, Marketing, Matplotlib, MongoDB, Monitoring, Networking, Pandas, Performance, Plotly, PostgreSQL, Python, REST, RF, SAP, SQL, Sales, Seaborn, Security, Spring, TCP/IP, Visualization, Windows, Word</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="AT42" t="inlineStr">
+        <is>
+          <t>JOB-925426C4</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="AV42" t="n">
+        <v>28.08</v>
+      </c>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Active Job</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:32:18</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>takudzwa manjonjo information systems graduate mimosa dalesford gweru manjonjotakudzwa gmail.com linkedin.com/in/takudzwa-manjonjo-b17bb631b professional profile results-driven hands-on support user access management administration standard cybersecurity practices such mccumber cube framework basic understanding data analysis visualisation python jupyter environments extracting transforming postgresql databases presenting actionable insights through tools pandas matplotlib seaborn plotly proficient microsoft windows environment office suite tcp/ip dns dhcp active directory fundamentals demonstrates technical knowledge java spring boot sql including olap operations mongodb rest api development code maven version control via git github proven record stabilising business-critical delivering measurable operational financial efficiencies public sector compliance cyber protection act chapter cobit adept translating solutions business value education master commerce degree expected july level midlands state university bachelor honours inter technology officer august bikita rural district council managed approximately system accounts implementing role-based controls password policies security procedures resulting zero recorded breaches unauthorised incidents administered maintained assets achieving asset accountability reducing loss probability less than extending equipment lifespan around preventative maintenance introduced service governance incident logging prioritisation escalation average response time hours under significantly improving end-user satisfaction freelance developer september present self-employed delivered end-to-end services installation configuration windows-based reliability productivity multiple clients ensuring secure usage aligned principles designed developed web-based applications restful apis supporting small digital delivery built relational non-relational modelling querying optimization performed extraction transformation within generate implemented visualization dashboards reports enabling make informed decisions configured troubleshot network ensure stable connectivity performance integrated supported accounting sage pastel belina transaction workflows reporting troubleshooting advised cloud-based saas scalability infrastructure costs collaborative applied best aligning zimbabwe</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:32:18</t>
+        </is>
+      </c>
+      <c r="BA42" t="inlineStr">
+        <is>
+          <t>Cvs_7_resume-167294743.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>APP-C4BC62B0</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ara5@gmail.com</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Tapiwa</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Chatara</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ara5@gmail.com</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>0774751372</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Harare</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Degree: Business Management and Information Technology (2017-2021) Class 2.1</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Degree</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>3</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Certified Information Security Manager (CISM)-PENDING</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>API, Active Directory, Backup, Business, C, C++, CI, Cloud, Communication, ERP, Git, Hardware, Helpdesk, Java, Less, Linux, Machine Learning, Marketing, Monitoring, Networking, SQL, SQL Server, Security, Telecom, Ubuntu, Windows, Wireless</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>1</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>45</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>58</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>58</v>
+      </c>
+      <c r="AT43" t="inlineStr">
+        <is>
+          <t>JOB-925426C4</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="AV43" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Active Job</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:32:22</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>nymegen road braeside harare phone email tapiwachatara5 gmail.com tapiwa chatara profile assistant jan dec results-driven ict professional proven supporting implementing minerals marketing corporation zimbabwe technology solutions within mining industrial environments skilled infrastructure management cybersecurity provided comprehensive support hardware software networking system administration project implementation adept integrating digital tools administered maintained sql databases ensure data integrity streamline operations enhance security operational efficiency resilience demanding managed vmware across linux microsoft windows ubuntu conditions demonstrates high systems analytical thinking collaborative approach supported erp user access aligned organizational objectives active directory services backups disaster recovery group auditor croco holdings conducted audits risk assessments identifying vulnerabilities recommending mitigation measures network protocols analyzed processes compliance auditing posture collaborated technical teams controls internal audit recommendations database server assurance omni contact bpo econet wireless maintenance reconciliation delivered hands-on business programming java vb.net connectivity uptime units web development troubleshot resolved incidents promptly minimize downtime cloud intern may virtualization mimosa company zvishavane gained departments helpdesk references telecommunications available upon request integration real-time monitoring reporting education degree information class catholic university certified cisa passed manager cism pending cissp api backup communication git less machine learning telecom</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:32:22</t>
+        </is>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>Cvs_7_resume-197759634.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>APP-A8ADB02D</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ttmakotore@gmail.com</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>TALENT</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TINOTENDA</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ttmakotore@gmail.com</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>0773 567 298</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Shona</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Diploma in Software Engineering</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Diploma/Certificate</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>16</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>I am a confident and dedicated software engineering graduate who is seeking to apply</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Business, C, C#, CI, Cisco, Communication, Go, HTML, IMS, Java, JavaScript, Machine Learning, Mobile, Node.js, PHP, SQL, Security, Testing, Windows</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>1</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>76</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="AT44" t="inlineStr">
+        <is>
+          <t>JOB-925426C4</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="AV44" t="n">
+        <v>29.81</v>
+      </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Active Job</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:32:28</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>talent tinotenda makotore mkoba gweru mobile e-mail ttmakotore gmail.com confident dedicated software engineering graduate who seeking apply advance through responsibility accountability looking being part working environment accommodates innovation freedom expression keenness learn aim stay date dynamic principles business thus taking achievement organisational objectives personal details d.o.b january marital status single languages fluent shona english sex male nationality zimbabwean driver license clean class organisation ekhonnector systems position ict intern period key duties developing web applications support organizational operations debugging troubleshooting issues existing testing ensure met providing technical internal external clients maintaining including installation backing database management user training cybersecurity awareness staff responding queries timely solutions assisting reviewing implementing policies procedures managing inherent risks within education tertiary level telone centre learning diploma certifications ethical hacking cisco progress february august zimsec ordinary nashville high school subjects maths computer science attributes detail oriented analytical problem solving diverse multicultural presentation communication goal planning self-motivated multitask under pressure honest confidential upholds ethics organised meets set deadlines intermediate graphic designing canva proficiency windows microsoft office packages understanding network fundamentals knowledge best practices programming java javascript sql php html referees philile cele supervisor email philah ekhonnector.co.za faith michael lecturer anashemichael tawanda mapuranga assistant manager tawanda.mapuranga telone.co.zw ims machine node.js security</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:32:28</t>
+        </is>
+      </c>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>Cvs_7_resume-304498731.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>APP-B6E2769C</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>mhiribidinelson@gmail.com</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Tungamirai</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Mhiribidi</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>mhiribidinelson@gmail.com</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>0718380556</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Highly motivated and technically versatile IT graduate with a Bachelor of Commerce; 2020-2023 Bachelor of Commerce in Catholic University of; Information Technology and Zimbabwe</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>HEMS AFRICA ENGINEERING Harare</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>ASIC, Business, C, CI, Excel, Firewall, Hardware, Helpdesk, IT Support, Linux, Machine Learning, Mobile, Monitoring, Networking, Other Tools, Outlook, RF, Router, Security, Switch, TCP/IP, Testing, Windows, Word</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="AT45" t="inlineStr">
+        <is>
+          <t>JOB-925426C4</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="AV45" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Active Job</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:32:32</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>tungamirai mhiribidi lavenham westgate harare mobile e-mail mhiribidinelson gmail.com professional summary highly motivated technically versatile graduate bachelor commerce information technology business management half industrial hands-on support systems administration networking user skilled troubleshooting hardware software network issues practical exposure microsoft environments system maintenance client strong learn quickly adapt new technologies effectively fast paced passionate infrastructure electronic security delivering reliable technical solutions core competencies windows installation configuration fundamentals tcp/ip dns dhcp router switch wi-fi setup cctv endpoint protection antivirus firewall remote onsite incident documentation reporting hems africa engineering january june intern provided first-line printing connectivity across multiple departments installed configured maintained desktops laptops assisted users password resets mailbox supported through printers scanners other peripheral devices end senior engineers during installations upgrades performed routine preventive equipment reduce downtime documented incidents configurations resolutions accurately delivered while maintaining excellent customer service standards basic camera monitoring key achievements accurate records efficient retrieval processes reduced recurring improving response procedures successfully over minimal escalation rates deploying configuring workstation setups within tight deadlines education institution catholic university zimbabwe second upper class proficiencies operating linux knowledge office suite outlook basics desktop laptop printer tools helpdesk/ticketing projects project small including routers switches access points conducted testing cable routing account creation onboarding activities references available upon request asic excel helpdesk machine learning word</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:32:32</t>
+        </is>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>Cvs_7_resume-431137323.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>APP-60D65269</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>resume</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>resume-</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>31</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>31</v>
+      </c>
+      <c r="AT46" t="inlineStr">
+        <is>
+          <t>JOB-925426C4</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="AV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Active Job</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:32:33</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:32:33</t>
+        </is>
+      </c>
+      <c r="BA46" t="inlineStr">
+        <is>
+          <t>Cvs_7_resume-444590916.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>APP-815F4725</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>claudiusmungu@gmail.com</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Highly</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>skilled</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>claudiusmungu@gmail.com</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>+263 785 279 654</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>63-4-7414</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Highly skilled Software Engineer and ICT professional with a Master's degree in Software Engineering; Master of Technology in Software Engineering; Bachelor of Technology Honors in Software Engineering; Certificate in Higher and Tertiary Education; Cisco Certified Network Associate (CCNA); Certificate in Mobile Software and Hardware - Ixar Technologies; Oracle Cloud Infrastructure Foundations Certified Associate</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>4</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Software Engineer | DevOps Specialist | Network Administrator</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Active Directory, Agile, Backup, Business, C, C++, CD, CI, CI/CD, CSS, Cisco, Cloud, Communication, DevOps, ERP, Firewall, Git, HTML, Hardware, IT Support, Integration Testing, Java, JavaScript, Less, Machine Learning, Mobile, Monitoring, Networking, Oracle, Performance, Project Management, Python, RF, Router, SQL, SQL Server, Security, Switch, Telecom, Testing, Tracing, VPN, VoIP, Vulnerability, Wireless, Word, iOS</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>45</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>61</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>61</v>
+      </c>
+      <c r="AT47" t="inlineStr">
+        <is>
+          <t>JOB-925426C4</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="AV47" t="n">
+        <v>48.08</v>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Active Job</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:32:38</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>george claudius mungundungundu software engineer devops specialist network administrator claudiusmungu gmail.com kuwadzana phase harare driver license class date birth march marital status single passport number emergency contact professional summary highly skilled ict master degree engineering over progressive development administration systems security proven expertise designing implementing robust infrastructure managing ci/cd pipelines ensuring comprehensive protocols certified cisco ccna oracle cloud demonstrated success leading digitization initiatives disaster-recovery plans optimizing system performance adept translating complex technical scalable solutions while maintaining strong focus quality assurance business continuity support part-time jan present granary medical centre configure maintain enterprise including firewalls anti-virus patch management design implement lan/wan architectures new facilities install cdma gpon vpn voip telecommunications equipment uptime optimize routers switches high-performance data transmission develop documentation guidelines hipaa compliance conduct awareness training programs staff best practices troubleshoot server issues minimal downtime hardware technician oct seveni group sql mission-critical applications automated backup erp sensitive patient test strategies cases reliability perform functional regression integration testing reducing production bugs execute scenarios covering both non-functional active directory services user accounts apply critical patches updates upgrades across monitor vulnerabilities intrusion detection scanning tools manage antivirus anti-malware deployments ensure licensing desktops laptops wireless networks printer servers pcs optimal sep jul city parking pvt ltd established administered policies protecting against internal external threats developed maintained disaster recovery hour time drafted aligned industry conducted employees procedures implemented preventive minimizing risk exposure performed regular audits vulnerability assessments graduate trainee managed organization-wide led all departments emphasis document accessibility structured cable installation termination following standards asset registers tracking</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:32:38</t>
+        </is>
+      </c>
+      <c r="BA47" t="inlineStr">
+        <is>
+          <t>Cvs_7_resume-448724203.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>APP-0BC576DF</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ions3@pjmzim.com</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>RUFARO</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TARUVINGA</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ions3@pjmzim.com</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>+263775504718</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>+263775504718 | rufarotn@gmail.com | Harare</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>+263775504718 | rufarotn@gmail.com | Harare, Zimbabwe | Male |; Single | Zimbabwean | Class 4 Driver’s License | DOB: 1990; thinking, excellent interpersonal skills and high- Gate Automation, Harare, Zimbabwe; • Certificate in Intruder Detection, Alarm,; CCTV, Access Control &amp; Biometric Systems PJM Security Installations, Harare, Zimbabwe; • National Diploma in Electronic Engineering • Installed barrier doors &amp; performed basic fabrication in the workshop; Bulawayo Polytechnic Zimbabwe Leaf Tobacco Co, Harare, Zimbabwe; 2004 - 2009 Ostande Investments, Gweru, Zimbabwe; Alcore Systems, Gweru, Zimbabwe; schematics, wiring, soldering) Aura Group, Gweru, Zimbabwe</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>23</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>ICT &amp; Electronics Technician with a strong</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>ARM, ASIC, Business, C, CI, ERP, Electrical Engineering, Electronics, Excel, Firewall, Hardware, IoT, Machine Learning, Marketing, Networking, PHP, RF, Router, Sales, Security, Word</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>88</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="AT48" t="inlineStr">
+        <is>
+          <t>JOB-925426C4</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="AV48" t="n">
+        <v>40.58</v>
+      </c>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Active Job</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:32:41</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>rufaro taruvinga summary rufarotn gmail.com harare zimbabwe male ict electronics technician strong single zimbabwean class driver license dob foundation technology operations customer support bringing hands-on problem solving abilities analytical critical creative thinking excellent interpersonal high gate automation quality calm honest when field installations jan explaining issues dedicated producing results installed configured intruder alarm cctv systems analog intercoms motors electric fences access control education ran structured cabling routers iot devices performed troubleshooting repairs certificate detection biometric pjm security institute electronic dec alarms national diploma engineering barrier doors basic fabrication workshop computer hexco bulawayo polytechnic leaf tobacco site risk april level subjects including mathematics managed scada system oversaw two heavy industrial sites science english adhered wan electrical room business studies geography protocol sheq training regular audits midlands christian college gweru ostande investments consultant may nov research identified implemented needs elv installation maintenance alcore networking addressing apr hardware software configuration participated marketing campaigns graphic designing cybersecurity host based firewalls preformed client end user device configurations malware removal password troubleshot network components low voltage interpreting schematics wiring soldering aura group microsoft office advanced pos knowledge deployed integrated terminals collaborated well prepared reports references state university dept feri sales technical lead attachment email installations3 pjmzim.com routine repair preventative printers audiovisual equipment deka human resources manager enhancing reliability infrastructure over workstations response assisted asset management inventory engineer makusha instructor cross-functional exposure dns dhcp ssh routing subnetting server room/ups web development php hapticsolutionszw microprocessor labs arm asic erp excel firewall machine learning router word</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:32:41</t>
+        </is>
+      </c>
+      <c r="BA48" t="inlineStr">
+        <is>
+          <t>Cvs_7_resume-490823847.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>APP-AA896EA8</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>chimukhombo@gmail.com</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>FARAI</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>PETER</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>chimukhombo@gmail.com</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>+263 78 093 2494</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>BSc (Honours) in Computer Systems Engineering</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Degree</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>2</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>FARAI PETER JUNIOR MUSHIPE</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>API, Android, C, CI, Cisco, Communication, DBA, Data Science, Firewall, Git, GitHub, Go, Hardware, IoT, Java, Leadership, Machine Learning, Messaging, Monitoring, Networking, PIC, Performance, Python, REST, RF, Router, Security, Selenium, Switch, TCP/IP, Windows</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>1</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="AT49" t="inlineStr">
+        <is>
+          <t>JOB-925426C4</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="AV49" t="n">
+        <v>39.42</v>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Active Job</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:33:12</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>farai peter junior mushipe electronic security support engineer network infrastructure cybersecurity mushipefarai01 gmail.com bulawayo zimbabwe available relocate harare portfolio faraimushipe.github.io credly https www.credly.com/users/farai-peter-jfarfar/badges professional summary bsc honours computer systems engineering graduate class midlands state university over live client-facing ict regulated financial services environment already operating level programme trains toward administering lan configuring routers switches deploying maintaining cctv managing pbx telephony delivering end-user technical across multiple sites holds cisco certifications fast learner who thrives hands environments works well independently eager expand microsoft administration sophos endpoint protection access control through structured development zhd networking tcp/ip dns dhcp lan/wan mikrotik routeros ubiquiti wi-fi installation configuration dahua cameras deployed surveillance system maintenance monitoring hardware windows troubleshooting component replacement preventive communications yeastar fanvil phones cpanel email compliance protocols firewall documentation incident reporting asset management remote anydesk teamviewer programming python java android sdk botpress selenium rest apis digital channel officer inclusive october present administer maintain branches routing traffic performance optimisation installed configured branch handling full deployment cabling ongoing phone supporting all internal inter-branch install configure troubleshoot windows-based printers peripherals user accounts corporate domains controls via hosting implement enforce rules policies perform routine corrective minimising downtime distributed document configurations changes resolutions accurate client-ready records deliver on-site resolution success rate end-to-end camera trainer revelo anthropic claude january march trained real github issues evaluating outputs identifying failure patterns iteratively improving model feedback rlhf produced detailed capturing behaviours improvement recommendations web scraping data mindrift toloka february built automation scripts collect process large-scale demonstrating strong scripting problem-solving independent working key projects</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:33:12</t>
+        </is>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>Cvs_7_resume-669698063.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>APP-E058C8ED</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>simba.rusike@gmail.com</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SIMBARASHE</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>RUSIKE</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>simba.rusike@gmail.com</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>+263 78 789 0123</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>SIMBARASHE RUSIKE; Name: Simbarashe Rusike; Nationality: Zimbabwean; Address: 18 Strathaven Road, Strathaven, Harare, Zimbabwe; Email: simba.rusike@gmail.com; LinkedIn: Simbarashe Rusike; Bachelor of Science Honours Degree in Mechatronics Engineering – National University of Science and Technology (NUST) (2021 to 2025); Certificate in Industrial Automation and PLC Programming (Siemens TIA Portal, 2024); Certificate in SolidWorks for Mechanical Design (Udemy, 2023); 1. Automation Engineering Intern – Delta Beverages Zimbabwe (January 2024 – June 2024)</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>24</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Hardware Engineering Student</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>ARM, ASIC, AutoCAD, C, CI, Electronics, Excel, Go, Hardware, Machine Learning, Mechatronics, Mobile, PCB, PLC, Router, SIEM, SolidWorks, Switch</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>88</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="AT50" t="inlineStr">
+        <is>
+          <t>JOB-925426C4</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="AV50" t="n">
+        <v>21.73</v>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Active Job</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:33:15</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>simbarashe rusike hardware engineering student personal details name d.o.b august sex male marital status single nationality zimbabwean contact address strathaven road harare zimbabwe mobile email simba.rusike gmail.com linkedin summary technically skilled engineer focus mechatronics robotics industrial automation systems bring strong combination mechanical intuition electronics knowledge deliver intelligent proactive problem-solver who thrives collaborative teams academic professional bachelor science honours degree national university technology nust certificate plc programming siemens tia portal solidworks design udemy advanced level petra high school masvingo mathematics physics technical drawing points ordinary ten passes projects axis cnc router build designed assembled desktop routing machine including stepper motor driver circuits limit switches custom controller pcb conveyor sorting system programmed s7-1200 automate belt colour inductive optical sensors inputs robotic arm prototype built dof servo-driven designing mounting structure pwm servo circuit arduino mega intern delta beverages january june assisted maintaining troubleshooting plc-controlled bottling line equipment supported commissioning new automated palletising unit conducted preventative maintenance checks sensor arrays actuator technician workshop laboratory staff setting calibrating machinery practical sessions maintained records usage consumables stock abilities ladder logic structured text scada basics hmi panel configuration control familiar autocad power kicad integration encoders proximity load cells thermocouples raspberry prototyping proficient microsoft office documentation career objective gain attachment where apply electromechanical contribute manufacturing efficiency excellence referees eng moyo head organisation phone nmoyo nust.ac.zw sibanda supervisor asibanda delta.co.zw asic excel learning siem switch</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:33:15</t>
+        </is>
+      </c>
+      <c r="BA50" t="inlineStr">
+        <is>
+          <t>Cvs_7_resume-714067111.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>APP-AE0410A0</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>nkakono68@gmail.com</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Norman</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Grassuance</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>nkakono68@gmail.com</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>+263771949995</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>12/11/2000</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>25</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Ruwa</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Address: 3375 Gora Crescent, Ruwa, Zimbabwe; Bachelors of Engineering Honours Degree in Computer Engineering December 2025; Degree Class: First Class (A-)</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>6</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Bachelors of Engineering Honours Degree in Computer Engineering December 2025</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>C, CI, Communication, Excel, Go, Hardware, IT Support, Linux, Machine Learning, Monitoring, Performance, RF, Security, Windows</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>1</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>62</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AT51" t="inlineStr">
+        <is>
+          <t>JOB-925426C4</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="AV51" t="n">
+        <v>22.88</v>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Active Job</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:33:18</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>norman grassuance kakono phone email nkakono68 gmail.com address gora crescent ruwa zimbabwe gender male d.o.b national driver license class professional profile dedicated detail-oriented ict graduate chinhoyi university technology hands-on support systems maintenance network administration strong foundation cybersecurity principles troubleshooting system optimization passionate leveraging improve organizational efficiency education bachelors engineering honours degree computer december first excellent tutorial college advanced level june passes physics chemistry rusununguko high school november mathematics ordinary including english technical hardware software configuration fundamentals risk identification protection operating windows linux repair web development monitoring performance intern aurex pvt limited feb maintained repaired equipment desktops laptops provided end users assisted configurations performed routine updates identified reported vulnerabilities key competencies problem solving analytical thinking teamwork collaboration communication attention detail adaptability willingness learn hobbies soccer reading coding travelling video games references isaac musuka officer contact number mrchimanyiwa lecturer excel machine learning security</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:33:18</t>
+        </is>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>Cvs_7_resume-769040377.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>APP-09B283E8</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>peacedambamuromo835@gmail.com</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Peace</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Dambamuromo</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>peacedambamuromo835@gmail.com</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>+263 78 674 3682</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>University of Zimbabwe 2025; BSc. Honours in Computer Engineering</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Motivated and hardworking Computer Engineering graduate seeking an opportunity as an IT Support &amp; Operations Assistant to</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>ASIC, Backup, C, CI, Cisco, EDA, Hardware, IT Support, Less, Machine Learning, Networking, Performance, RF, Router, Security, Switch, VLAN, Wireless, Word</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="AT52" t="inlineStr">
+        <is>
+          <t>JOB-925426C4</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="AV52" t="n">
+        <v>23.46</v>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Active Job</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:33:23</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>peace dambamuromo hatcliffe extension harare peacedambamuromo835 gmail.com objective motivated hardworking computer engineering graduate seeking opportunity support operations assistant apply technical knowledge problem-solving abilities strong ethic professional environment while gaining hands industry education university zimbabwe bsc honours city council june may provided day-to-day staff troubleshooting hardware software network-related issues installed configured maintained desktop computers laptops printers other office equipment assisted users installation password resets email setup system access monitored local area network connectivity internet conducted routine updates backups antivirus checks ensure security performance maintaining cctv systems problems supported configuration routers switches wireless points recorded tracked ensured timely resolution requests inventory management accessories worked closely senior personnel during maintenance upgrades operational tasks networking fundamentals device user assistance basic cybersecurity microsoft suite backup router switch clear documentation collaboration projects troubleshot practicals addressing vlans routing configurations performed hardware-related certifications cisco certified associate ccna progress subnetting switching concepts basics methodologies reference available upon request asic eda less machine learning vlan word</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:33:23</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>Cvs_7_resume-997097551.pdf</t>
         </is>
       </c>
     </row>

--- a/cv_analyzer/data/applicants.xlsx
+++ b/cv_analyzer/data/applicants.xlsx
@@ -15605,22 +15605,22 @@
         <v>5</v>
       </c>
       <c r="AN77" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO77" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AP77" t="n">
         <v>30</v>
       </c>
       <c r="AQ77" t="n">
-        <v>54</v>
+        <v>47.8</v>
       </c>
       <c r="AR77" t="n">
         <v>100</v>
       </c>
       <c r="AS77" t="n">
-        <v>54</v>
+        <v>47.8</v>
       </c>
       <c r="AT77" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>5</v>
       </c>
       <c r="AN78" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO78" t="n">
         <v>28</v>
@@ -15813,13 +15813,13 @@
         <v>30</v>
       </c>
       <c r="AQ78" t="n">
-        <v>56.6</v>
+        <v>54.2</v>
       </c>
       <c r="AR78" t="n">
         <v>100</v>
       </c>
       <c r="AS78" t="n">
-        <v>56.6</v>
+        <v>54.2</v>
       </c>
       <c r="AT78" t="inlineStr">
         <is>
@@ -16003,22 +16003,22 @@
         <v>5</v>
       </c>
       <c r="AN79" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AO79" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="AP79" t="n">
         <v>30</v>
       </c>
       <c r="AQ79" t="n">
-        <v>67.59999999999999</v>
+        <v>58</v>
       </c>
       <c r="AR79" t="n">
         <v>100</v>
       </c>
       <c r="AS79" t="n">
-        <v>67.59999999999999</v>
+        <v>58</v>
       </c>
       <c r="AT79" t="inlineStr">
         <is>
@@ -16206,22 +16206,22 @@
         <v>5</v>
       </c>
       <c r="AN80" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO80" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="AP80" t="n">
         <v>30</v>
       </c>
       <c r="AQ80" t="n">
-        <v>85.2</v>
+        <v>78.2</v>
       </c>
       <c r="AR80" t="n">
         <v>100</v>
       </c>
       <c r="AS80" t="n">
-        <v>85.2</v>
+        <v>78.2</v>
       </c>
       <c r="AT80" t="inlineStr">
         <is>
@@ -16409,22 +16409,22 @@
         <v>5</v>
       </c>
       <c r="AN81" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO81" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="AP81" t="n">
         <v>30</v>
       </c>
       <c r="AQ81" t="n">
-        <v>69.59999999999999</v>
+        <v>61</v>
       </c>
       <c r="AR81" t="n">
         <v>100</v>
       </c>
       <c r="AS81" t="n">
-        <v>69.59999999999999</v>
+        <v>61</v>
       </c>
       <c r="AT81" t="inlineStr">
         <is>
@@ -16608,22 +16608,22 @@
         <v>5</v>
       </c>
       <c r="AN82" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO82" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AP82" t="n">
         <v>30</v>
       </c>
       <c r="AQ82" t="n">
-        <v>85.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="AR82" t="n">
         <v>100</v>
       </c>
       <c r="AS82" t="n">
-        <v>85.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="AT82" t="inlineStr">
         <is>
@@ -16810,19 +16810,19 @@
         <v>50</v>
       </c>
       <c r="AO83" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="AP83" t="n">
         <v>30</v>
       </c>
       <c r="AQ83" t="n">
-        <v>53.8</v>
+        <v>49</v>
       </c>
       <c r="AR83" t="n">
         <v>100</v>
       </c>
       <c r="AS83" t="n">
-        <v>53.8</v>
+        <v>49</v>
       </c>
       <c r="AT83" t="inlineStr">
         <is>
@@ -17006,22 +17006,22 @@
         <v>5</v>
       </c>
       <c r="AN84" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="AO84" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AP84" t="n">
         <v>30</v>
       </c>
       <c r="AQ84" t="n">
-        <v>77.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AR84" t="n">
         <v>100</v>
       </c>
       <c r="AS84" t="n">
-        <v>77.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AT84" t="inlineStr">
         <is>
@@ -17205,22 +17205,22 @@
         <v>5</v>
       </c>
       <c r="AN85" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO85" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="AP85" t="n">
         <v>30</v>
       </c>
       <c r="AQ85" t="n">
-        <v>84.8</v>
+        <v>78.2</v>
       </c>
       <c r="AR85" t="n">
         <v>100</v>
       </c>
       <c r="AS85" t="n">
-        <v>84.8</v>
+        <v>78.2</v>
       </c>
       <c r="AT85" t="inlineStr">
         <is>
@@ -17407,19 +17407,19 @@
         <v>80</v>
       </c>
       <c r="AO86" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="AP86" t="n">
         <v>30</v>
       </c>
       <c r="AQ86" t="n">
-        <v>60.8</v>
+        <v>58</v>
       </c>
       <c r="AR86" t="n">
         <v>100</v>
       </c>
       <c r="AS86" t="n">
-        <v>60.8</v>
+        <v>58</v>
       </c>
       <c r="AT86" t="inlineStr">
         <is>
@@ -17606,19 +17606,19 @@
         <v>80</v>
       </c>
       <c r="AO87" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AP87" t="n">
         <v>30</v>
       </c>
       <c r="AQ87" t="n">
-        <v>48.4</v>
+        <v>44.8</v>
       </c>
       <c r="AR87" t="n">
         <v>100</v>
       </c>
       <c r="AS87" t="n">
-        <v>48.4</v>
+        <v>44.8</v>
       </c>
       <c r="AT87" t="inlineStr">
         <is>
@@ -17798,22 +17798,22 @@
         <v>5</v>
       </c>
       <c r="AN88" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO88" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="AP88" t="n">
         <v>30</v>
       </c>
       <c r="AQ88" t="n">
-        <v>85.2</v>
+        <v>78.2</v>
       </c>
       <c r="AR88" t="n">
         <v>100</v>
       </c>
       <c r="AS88" t="n">
-        <v>85.2</v>
+        <v>78.2</v>
       </c>
       <c r="AT88" t="inlineStr">
         <is>
@@ -17996,19 +17996,19 @@
         <v>80</v>
       </c>
       <c r="AO89" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AP89" t="n">
         <v>30</v>
       </c>
       <c r="AQ89" t="n">
-        <v>48.4</v>
+        <v>44.8</v>
       </c>
       <c r="AR89" t="n">
         <v>100</v>
       </c>
       <c r="AS89" t="n">
-        <v>48.4</v>
+        <v>44.8</v>
       </c>
       <c r="AT89" t="inlineStr">
         <is>
@@ -18192,22 +18192,22 @@
         <v>5</v>
       </c>
       <c r="AN90" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="AO90" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="AP90" t="n">
         <v>30</v>
       </c>
       <c r="AQ90" t="n">
-        <v>73.40000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="AR90" t="n">
         <v>100</v>
       </c>
       <c r="AS90" t="n">
-        <v>73.40000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="AT90" t="inlineStr">
         <is>
@@ -18391,22 +18391,22 @@
         <v>5</v>
       </c>
       <c r="AN91" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO91" t="n">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="AP91" t="n">
         <v>30</v>
       </c>
       <c r="AQ91" t="n">
-        <v>83.2</v>
+        <v>67.8</v>
       </c>
       <c r="AR91" t="n">
         <v>100</v>
       </c>
       <c r="AS91" t="n">
-        <v>83.2</v>
+        <v>67.8</v>
       </c>
       <c r="AT91" t="inlineStr">
         <is>
@@ -18586,22 +18586,22 @@
         <v>5</v>
       </c>
       <c r="AN92" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO92" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="AP92" t="n">
         <v>30</v>
       </c>
       <c r="AQ92" t="n">
-        <v>86</v>
+        <v>67.8</v>
       </c>
       <c r="AR92" t="n">
         <v>100</v>
       </c>
       <c r="AS92" t="n">
-        <v>86</v>
+        <v>67.8</v>
       </c>
       <c r="AT92" t="inlineStr">
         <is>
@@ -18781,22 +18781,22 @@
         <v>5</v>
       </c>
       <c r="AN93" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO93" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AP93" t="n">
         <v>30</v>
       </c>
       <c r="AQ93" t="n">
-        <v>85.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AR93" t="n">
         <v>100</v>
       </c>
       <c r="AS93" t="n">
-        <v>85.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AT93" t="inlineStr">
         <is>
@@ -18980,22 +18980,22 @@
         <v>5</v>
       </c>
       <c r="AN94" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AO94" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="AP94" t="n">
         <v>30</v>
       </c>
       <c r="AQ94" t="n">
-        <v>67.2</v>
+        <v>51.2</v>
       </c>
       <c r="AR94" t="n">
         <v>100</v>
       </c>
       <c r="AS94" t="n">
-        <v>67.2</v>
+        <v>51.2</v>
       </c>
       <c r="AT94" t="inlineStr">
         <is>
@@ -19179,22 +19179,22 @@
         <v>5</v>
       </c>
       <c r="AN95" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AO95" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="AP95" t="n">
         <v>30</v>
       </c>
       <c r="AQ95" t="n">
-        <v>58.4</v>
+        <v>44.8</v>
       </c>
       <c r="AR95" t="n">
         <v>100</v>
       </c>
       <c r="AS95" t="n">
-        <v>58.4</v>
+        <v>44.8</v>
       </c>
       <c r="AT95" t="inlineStr">
         <is>
@@ -19377,19 +19377,19 @@
         <v>90</v>
       </c>
       <c r="AO96" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AP96" t="n">
         <v>30</v>
       </c>
       <c r="AQ96" t="n">
-        <v>56.6</v>
+        <v>54.2</v>
       </c>
       <c r="AR96" t="n">
         <v>100</v>
       </c>
       <c r="AS96" t="n">
-        <v>56.6</v>
+        <v>54.2</v>
       </c>
       <c r="AT96" t="inlineStr">
         <is>
@@ -19573,22 +19573,22 @@
         <v>5</v>
       </c>
       <c r="AN97" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO97" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AP97" t="n">
         <v>30</v>
       </c>
       <c r="AQ97" t="n">
-        <v>86</v>
+        <v>78.2</v>
       </c>
       <c r="AR97" t="n">
         <v>100</v>
       </c>
       <c r="AS97" t="n">
-        <v>86</v>
+        <v>78.2</v>
       </c>
       <c r="AT97" t="inlineStr">
         <is>
@@ -19779,19 +19779,19 @@
         <v>80</v>
       </c>
       <c r="AO98" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AP98" t="n">
         <v>30</v>
       </c>
       <c r="AQ98" t="n">
-        <v>55.2</v>
+        <v>51.2</v>
       </c>
       <c r="AR98" t="n">
         <v>100</v>
       </c>
       <c r="AS98" t="n">
-        <v>55.2</v>
+        <v>51.2</v>
       </c>
       <c r="AT98" t="inlineStr">
         <is>
@@ -19975,22 +19975,22 @@
         <v>5</v>
       </c>
       <c r="AN99" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO99" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="AP99" t="n">
         <v>30</v>
       </c>
       <c r="AQ99" t="n">
-        <v>67.59999999999999</v>
+        <v>61</v>
       </c>
       <c r="AR99" t="n">
         <v>100</v>
       </c>
       <c r="AS99" t="n">
-        <v>67.59999999999999</v>
+        <v>61</v>
       </c>
       <c r="AT99" t="inlineStr">
         <is>
@@ -20177,19 +20177,19 @@
         <v>50</v>
       </c>
       <c r="AO100" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AP100" t="n">
         <v>30</v>
       </c>
       <c r="AQ100" t="n">
-        <v>44.6</v>
+        <v>42.2</v>
       </c>
       <c r="AR100" t="n">
         <v>100</v>
       </c>
       <c r="AS100" t="n">
-        <v>44.6</v>
+        <v>42.2</v>
       </c>
       <c r="AT100" t="inlineStr">
         <is>
@@ -20376,19 +20376,19 @@
         <v>90</v>
       </c>
       <c r="AO101" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AP101" t="n">
         <v>30</v>
       </c>
       <c r="AQ101" t="n">
-        <v>51.4</v>
+        <v>47.8</v>
       </c>
       <c r="AR101" t="n">
         <v>100</v>
       </c>
       <c r="AS101" t="n">
-        <v>51.4</v>
+        <v>47.8</v>
       </c>
       <c r="AT101" t="inlineStr">
         <is>
@@ -20575,19 +20575,19 @@
         <v>80</v>
       </c>
       <c r="AO102" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AP102" t="n">
         <v>30</v>
       </c>
       <c r="AQ102" t="n">
-        <v>80</v>
+        <v>75.2</v>
       </c>
       <c r="AR102" t="n">
         <v>100</v>
       </c>
       <c r="AS102" t="n">
-        <v>80</v>
+        <v>75.2</v>
       </c>
       <c r="AT102" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>5</v>
       </c>
       <c r="AN103" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AO103" t="n">
         <v>45</v>
@@ -20776,13 +20776,13 @@
         <v>30</v>
       </c>
       <c r="AQ103" t="n">
-        <v>60.4</v>
+        <v>58</v>
       </c>
       <c r="AR103" t="n">
         <v>100</v>
       </c>
       <c r="AS103" t="n">
-        <v>60.4</v>
+        <v>58</v>
       </c>
       <c r="AT103" t="inlineStr">
         <is>
@@ -20966,22 +20966,22 @@
         <v>5</v>
       </c>
       <c r="AN104" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AO104" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="AP104" t="n">
         <v>30</v>
       </c>
       <c r="AQ104" t="n">
-        <v>58.5</v>
+        <v>51.2</v>
       </c>
       <c r="AR104" t="n">
         <v>100</v>
       </c>
       <c r="AS104" t="n">
-        <v>58.5</v>
+        <v>51.2</v>
       </c>
       <c r="AT104" t="inlineStr">
         <is>
@@ -21165,22 +21165,22 @@
         <v>5</v>
       </c>
       <c r="AN105" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AO105" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AP105" t="n">
         <v>30</v>
       </c>
       <c r="AQ105" t="n">
-        <v>76.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AR105" t="n">
         <v>100</v>
       </c>
       <c r="AS105" t="n">
-        <v>76.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AT105" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>5</v>
       </c>
       <c r="AN106" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO106" t="n">
         <v>28</v>
@@ -21369,13 +21369,13 @@
         <v>30</v>
       </c>
       <c r="AQ106" t="n">
-        <v>56.6</v>
+        <v>54.2</v>
       </c>
       <c r="AR106" t="n">
         <v>100</v>
       </c>
       <c r="AS106" t="n">
-        <v>56.6</v>
+        <v>54.2</v>
       </c>
       <c r="AT106" t="inlineStr">
         <is>
@@ -21559,22 +21559,22 @@
         <v>5</v>
       </c>
       <c r="AN107" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO107" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AP107" t="n">
         <v>30</v>
       </c>
       <c r="AQ107" t="n">
-        <v>67.40000000000001</v>
+        <v>61</v>
       </c>
       <c r="AR107" t="n">
         <v>100</v>
       </c>
       <c r="AS107" t="n">
-        <v>67.40000000000001</v>
+        <v>61</v>
       </c>
       <c r="AT107" t="inlineStr">
         <is>
@@ -21758,22 +21758,22 @@
         <v>5</v>
       </c>
       <c r="AN108" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="AO108" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="AP108" t="n">
         <v>30</v>
       </c>
       <c r="AQ108" t="n">
-        <v>50.6</v>
+        <v>42.2</v>
       </c>
       <c r="AR108" t="n">
         <v>100</v>
       </c>
       <c r="AS108" t="n">
-        <v>50.6</v>
+        <v>42.2</v>
       </c>
       <c r="AT108" t="inlineStr">
         <is>
@@ -21956,19 +21956,19 @@
         <v>80</v>
       </c>
       <c r="AO109" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="AP109" t="n">
         <v>30</v>
       </c>
       <c r="AQ109" t="n">
-        <v>54.8</v>
+        <v>51.2</v>
       </c>
       <c r="AR109" t="n">
         <v>100</v>
       </c>
       <c r="AS109" t="n">
-        <v>54.8</v>
+        <v>51.2</v>
       </c>
       <c r="AT109" t="inlineStr">
         <is>
@@ -22155,19 +22155,19 @@
         <v>80</v>
       </c>
       <c r="AO110" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AP110" t="n">
         <v>30</v>
       </c>
       <c r="AQ110" t="n">
-        <v>56.8</v>
+        <v>51.2</v>
       </c>
       <c r="AR110" t="n">
         <v>100</v>
       </c>
       <c r="AS110" t="n">
-        <v>56.8</v>
+        <v>51.2</v>
       </c>
       <c r="AT110" t="inlineStr">
         <is>
@@ -22351,22 +22351,22 @@
         <v>5</v>
       </c>
       <c r="AN111" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO111" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AP111" t="n">
         <v>30</v>
       </c>
       <c r="AQ111" t="n">
-        <v>86</v>
+        <v>78.2</v>
       </c>
       <c r="AR111" t="n">
         <v>100</v>
       </c>
       <c r="AS111" t="n">
-        <v>86</v>
+        <v>78.2</v>
       </c>
       <c r="AT111" t="inlineStr">
         <is>
@@ -22553,19 +22553,19 @@
         <v>90</v>
       </c>
       <c r="AO112" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AP112" t="n">
         <v>30</v>
       </c>
       <c r="AQ112" t="n">
-        <v>59.8</v>
+        <v>54.2</v>
       </c>
       <c r="AR112" t="n">
         <v>100</v>
       </c>
       <c r="AS112" t="n">
-        <v>59.8</v>
+        <v>54.2</v>
       </c>
       <c r="AT112" t="inlineStr">
         <is>
@@ -22749,22 +22749,22 @@
         <v>5</v>
       </c>
       <c r="AN113" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AO113" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AP113" t="n">
         <v>30</v>
       </c>
       <c r="AQ113" t="n">
-        <v>62.4</v>
+        <v>58</v>
       </c>
       <c r="AR113" t="n">
         <v>100</v>
       </c>
       <c r="AS113" t="n">
-        <v>62.4</v>
+        <v>58</v>
       </c>
       <c r="AT113" t="inlineStr">
         <is>
@@ -22951,19 +22951,19 @@
         <v>90</v>
       </c>
       <c r="AO114" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AP114" t="n">
         <v>30</v>
       </c>
       <c r="AQ114" t="n">
-        <v>83</v>
+        <v>78.2</v>
       </c>
       <c r="AR114" t="n">
         <v>100</v>
       </c>
       <c r="AS114" t="n">
-        <v>83</v>
+        <v>78.2</v>
       </c>
       <c r="AT114" t="inlineStr">
         <is>
@@ -23151,22 +23151,22 @@
         <v>5</v>
       </c>
       <c r="AN115" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO115" t="n">
         <v>88</v>
-      </c>
-      <c r="AO115" t="n">
-        <v>96</v>
       </c>
       <c r="AP115" t="n">
         <v>30</v>
       </c>
       <c r="AQ115" t="n">
-        <v>80.8</v>
+        <v>75.2</v>
       </c>
       <c r="AR115" t="n">
         <v>100</v>
       </c>
       <c r="AS115" t="n">
-        <v>80.8</v>
+        <v>75.2</v>
       </c>
       <c r="AT115" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>5</v>
       </c>
       <c r="AN116" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="AO116" t="n">
         <v>62</v>
@@ -23363,13 +23363,13 @@
         <v>30</v>
       </c>
       <c r="AQ116" t="n">
-        <v>60.6</v>
+        <v>55.8</v>
       </c>
       <c r="AR116" t="n">
         <v>100</v>
       </c>
       <c r="AS116" t="n">
-        <v>60.6</v>
+        <v>55.8</v>
       </c>
       <c r="AT116" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
         <v>5</v>
       </c>
       <c r="AN117" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="AO117" t="n">
         <v>88</v>
@@ -23562,13 +23562,13 @@
         <v>30</v>
       </c>
       <c r="AQ117" t="n">
-        <v>68.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="AR117" t="n">
         <v>100</v>
       </c>
       <c r="AS117" t="n">
-        <v>68.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="AT117" t="inlineStr">
         <is>
@@ -23752,22 +23752,22 @@
         <v>5</v>
       </c>
       <c r="AN118" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO118" t="n">
         <v>88</v>
-      </c>
-      <c r="AO118" t="n">
-        <v>100</v>
       </c>
       <c r="AP118" t="n">
         <v>30</v>
       </c>
       <c r="AQ118" t="n">
-        <v>82.40000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="AR118" t="n">
         <v>100</v>
       </c>
       <c r="AS118" t="n">
-        <v>82.40000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="AT118" t="inlineStr">
         <is>
@@ -23954,19 +23954,19 @@
         <v>80</v>
       </c>
       <c r="AO119" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AP119" t="n">
         <v>30</v>
       </c>
       <c r="AQ119" t="n">
-        <v>73.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AR119" t="n">
         <v>100</v>
       </c>
       <c r="AS119" t="n">
-        <v>73.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AT119" t="inlineStr">
         <is>
@@ -24153,19 +24153,19 @@
         <v>90</v>
       </c>
       <c r="AO120" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP120" t="n">
         <v>30</v>
       </c>
       <c r="AQ120" t="n">
-        <v>47.4</v>
+        <v>47.8</v>
       </c>
       <c r="AR120" t="n">
         <v>100</v>
       </c>
       <c r="AS120" t="n">
-        <v>47.4</v>
+        <v>47.8</v>
       </c>
       <c r="AT120" t="inlineStr">
         <is>

--- a/cv_analyzer/data/applicants.xlsx
+++ b/cv_analyzer/data/applicants.xlsx
@@ -832,22 +832,22 @@
         <v>5</v>
       </c>
       <c r="AN2" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO2" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="AP2" t="n">
         <v>30</v>
       </c>
       <c r="AQ2" t="n">
-        <v>73.40000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="AR2" t="n">
         <v>100</v>
       </c>
       <c r="AS2" t="n">
-        <v>73.40000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -996,25 +996,25 @@
         <v>5</v>
       </c>
       <c r="AM3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AN3" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="AO3" t="n">
         <v>12</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16.3</v>
+        <v>32.8</v>
       </c>
       <c r="AR3" t="n">
         <v>100</v>
       </c>
       <c r="AS3" t="n">
-        <v>16.3</v>
+        <v>32.8</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1193,19 +1193,19 @@
         <v>80</v>
       </c>
       <c r="AO4" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="AP4" t="n">
         <v>30</v>
       </c>
       <c r="AQ4" t="n">
-        <v>56</v>
+        <v>44.8</v>
       </c>
       <c r="AR4" t="n">
         <v>100</v>
       </c>
       <c r="AS4" t="n">
-        <v>56</v>
+        <v>44.8</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1392,19 +1392,19 @@
         <v>80</v>
       </c>
       <c r="AO5" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="AP5" t="n">
         <v>30</v>
       </c>
       <c r="AQ5" t="n">
-        <v>63.6</v>
+        <v>58</v>
       </c>
       <c r="AR5" t="n">
         <v>100</v>
       </c>
       <c r="AS5" t="n">
-        <v>63.6</v>
+        <v>58</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1779,22 +1779,22 @@
         <v>5</v>
       </c>
       <c r="AN7" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="AO7" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AP7" t="n">
         <v>30</v>
       </c>
       <c r="AQ7" t="n">
-        <v>75.8</v>
+        <v>66.2</v>
       </c>
       <c r="AR7" t="n">
         <v>100</v>
       </c>
       <c r="AS7" t="n">
-        <v>75.8</v>
+        <v>66.2</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1978,22 +1978,22 @@
         <v>5</v>
       </c>
       <c r="AN8" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO8" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="AP8" t="n">
         <v>30</v>
       </c>
       <c r="AQ8" t="n">
-        <v>74.2</v>
+        <v>67.8</v>
       </c>
       <c r="AR8" t="n">
         <v>100</v>
       </c>
       <c r="AS8" t="n">
-        <v>74.2</v>
+        <v>67.8</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -2176,19 +2176,19 @@
         <v>50</v>
       </c>
       <c r="AO9" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="AP9" t="n">
         <v>30</v>
       </c>
       <c r="AQ9" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="AR9" t="n">
         <v>100</v>
       </c>
       <c r="AS9" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
@@ -2368,22 +2368,22 @@
         <v>5</v>
       </c>
       <c r="AN10" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="AO10" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="AP10" t="n">
         <v>30</v>
       </c>
       <c r="AQ10" t="n">
-        <v>70.8</v>
+        <v>58</v>
       </c>
       <c r="AR10" t="n">
         <v>100</v>
       </c>
       <c r="AS10" t="n">
-        <v>70.8</v>
+        <v>58</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2570,19 +2570,19 @@
         <v>90</v>
       </c>
       <c r="AO11" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="AP11" t="n">
         <v>30</v>
       </c>
       <c r="AQ11" t="n">
-        <v>57</v>
+        <v>54.2</v>
       </c>
       <c r="AR11" t="n">
         <v>100</v>
       </c>
       <c r="AS11" t="n">
-        <v>57</v>
+        <v>54.2</v>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
@@ -2766,22 +2766,22 @@
         <v>5</v>
       </c>
       <c r="AN12" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AO12" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="AP12" t="n">
         <v>30</v>
       </c>
       <c r="AQ12" t="n">
-        <v>67.59999999999999</v>
+        <v>58</v>
       </c>
       <c r="AR12" t="n">
         <v>100</v>
       </c>
       <c r="AS12" t="n">
-        <v>67.59999999999999</v>
+        <v>58</v>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>5</v>
       </c>
       <c r="AN13" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO13" t="n">
         <v>12</v>
@@ -2974,13 +2974,13 @@
         <v>30</v>
       </c>
       <c r="AQ13" t="n">
-        <v>50.8</v>
+        <v>47.8</v>
       </c>
       <c r="AR13" t="n">
         <v>100</v>
       </c>
       <c r="AS13" t="n">
-        <v>50.8</v>
+        <v>47.8</v>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
@@ -3164,22 +3164,22 @@
         <v>5</v>
       </c>
       <c r="AN14" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO14" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="AP14" t="n">
         <v>30</v>
       </c>
       <c r="AQ14" t="n">
-        <v>83.8</v>
+        <v>78.2</v>
       </c>
       <c r="AR14" t="n">
         <v>100</v>
       </c>
       <c r="AS14" t="n">
-        <v>83.8</v>
+        <v>78.2</v>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
@@ -3359,22 +3359,22 @@
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO15" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="AP15" t="n">
         <v>30</v>
       </c>
       <c r="AQ15" t="n">
-        <v>60.2</v>
+        <v>54.2</v>
       </c>
       <c r="AR15" t="n">
         <v>100</v>
       </c>
       <c r="AS15" t="n">
-        <v>60.2</v>
+        <v>54.2</v>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
@@ -3565,19 +3565,19 @@
         <v>90</v>
       </c>
       <c r="AO16" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AP16" t="n">
         <v>30</v>
       </c>
       <c r="AQ16" t="n">
-        <v>67.40000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="AR16" t="n">
         <v>100</v>
       </c>
       <c r="AS16" t="n">
-        <v>67.40000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
@@ -3761,22 +3761,22 @@
         <v>5</v>
       </c>
       <c r="AN17" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="AO17" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AP17" t="n">
         <v>30</v>
       </c>
       <c r="AQ17" t="n">
-        <v>42.2</v>
+        <v>35.8</v>
       </c>
       <c r="AR17" t="n">
         <v>100</v>
       </c>
       <c r="AS17" t="n">
-        <v>42.2</v>
+        <v>35.8</v>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>5</v>
       </c>
       <c r="AN18" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AO18" t="n">
         <v>28</v>
@@ -3969,13 +3969,13 @@
         <v>30</v>
       </c>
       <c r="AQ18" t="n">
-        <v>57.2</v>
+        <v>51.2</v>
       </c>
       <c r="AR18" t="n">
         <v>100</v>
       </c>
       <c r="AS18" t="n">
-        <v>57.2</v>
+        <v>51.2</v>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
@@ -4152,25 +4152,25 @@
         <v>5</v>
       </c>
       <c r="AM19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AN19" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO19" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="AP19" t="n">
         <v>30</v>
       </c>
       <c r="AQ19" t="n">
-        <v>80.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="AR19" t="n">
         <v>100</v>
       </c>
       <c r="AS19" t="n">
-        <v>80.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
@@ -4354,22 +4354,22 @@
         <v>5</v>
       </c>
       <c r="AN20" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO20" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AP20" t="n">
         <v>30</v>
       </c>
       <c r="AQ20" t="n">
-        <v>85.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="AR20" t="n">
         <v>100</v>
       </c>
       <c r="AS20" t="n">
-        <v>85.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
@@ -4553,22 +4553,22 @@
         <v>5</v>
       </c>
       <c r="AN21" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO21" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="AP21" t="n">
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>57.8</v>
+        <v>47.8</v>
       </c>
       <c r="AR21" t="n">
         <v>100</v>
       </c>
       <c r="AS21" t="n">
-        <v>57.8</v>
+        <v>47.8</v>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
@@ -4752,22 +4752,22 @@
         <v>5</v>
       </c>
       <c r="AN22" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO22" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="AP22" t="n">
         <v>30</v>
       </c>
       <c r="AQ22" t="n">
-        <v>56.8</v>
+        <v>47.8</v>
       </c>
       <c r="AR22" t="n">
         <v>100</v>
       </c>
       <c r="AS22" t="n">
-        <v>56.8</v>
+        <v>47.8</v>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
@@ -4951,22 +4951,22 @@
         <v>5</v>
       </c>
       <c r="AN23" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="AO23" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AP23" t="n">
         <v>30</v>
       </c>
       <c r="AQ23" t="n">
-        <v>43</v>
+        <v>35.8</v>
       </c>
       <c r="AR23" t="n">
         <v>100</v>
       </c>
       <c r="AS23" t="n">
-        <v>43</v>
+        <v>35.8</v>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>5</v>
       </c>
       <c r="AN24" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO24" t="n">
         <v>28</v>
@@ -5159,13 +5159,13 @@
         <v>30</v>
       </c>
       <c r="AQ24" t="n">
-        <v>57.2</v>
+        <v>54.2</v>
       </c>
       <c r="AR24" t="n">
         <v>100</v>
       </c>
       <c r="AS24" t="n">
-        <v>57.2</v>
+        <v>54.2</v>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
@@ -5349,22 +5349,22 @@
         <v>5</v>
       </c>
       <c r="AN25" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="AO25" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AP25" t="n">
         <v>30</v>
       </c>
       <c r="AQ25" t="n">
-        <v>77.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AR25" t="n">
         <v>100</v>
       </c>
       <c r="AS25" t="n">
-        <v>77.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
@@ -5548,22 +5548,22 @@
         <v>5</v>
       </c>
       <c r="AN26" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO26" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AP26" t="n">
         <v>30</v>
       </c>
       <c r="AQ26" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="AR26" t="n">
         <v>100</v>
       </c>
       <c r="AS26" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
@@ -5743,22 +5743,22 @@
         <v>5</v>
       </c>
       <c r="AN27" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO27" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="AP27" t="n">
         <v>30</v>
       </c>
       <c r="AQ27" t="n">
-        <v>74.2</v>
+        <v>67.8</v>
       </c>
       <c r="AR27" t="n">
         <v>100</v>
       </c>
       <c r="AS27" t="n">
-        <v>74.2</v>
+        <v>67.8</v>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
@@ -5938,22 +5938,22 @@
         <v>5</v>
       </c>
       <c r="AN28" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO28" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AP28" t="n">
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>86</v>
+        <v>78.2</v>
       </c>
       <c r="AR28" t="n">
         <v>100</v>
       </c>
       <c r="AS28" t="n">
-        <v>86</v>
+        <v>78.2</v>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>5</v>
       </c>
       <c r="AN29" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AO29" t="n">
         <v>28</v>
@@ -6146,13 +6146,13 @@
         <v>30</v>
       </c>
       <c r="AQ29" t="n">
-        <v>57.2</v>
+        <v>51.2</v>
       </c>
       <c r="AR29" t="n">
         <v>100</v>
       </c>
       <c r="AS29" t="n">
-        <v>57.2</v>
+        <v>51.2</v>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
@@ -6336,22 +6336,22 @@
         <v>5</v>
       </c>
       <c r="AN30" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="AO30" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="AP30" t="n">
         <v>30</v>
       </c>
       <c r="AQ30" t="n">
-        <v>72</v>
+        <v>64.8</v>
       </c>
       <c r="AR30" t="n">
         <v>100</v>
       </c>
       <c r="AS30" t="n">
-        <v>72</v>
+        <v>64.8</v>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
@@ -6535,22 +6535,22 @@
         <v>5</v>
       </c>
       <c r="AN31" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="AO31" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AP31" t="n">
         <v>30</v>
       </c>
       <c r="AQ31" t="n">
-        <v>29.3</v>
+        <v>35.8</v>
       </c>
       <c r="AR31" t="n">
         <v>100</v>
       </c>
       <c r="AS31" t="n">
-        <v>29.3</v>
+        <v>35.8</v>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
@@ -6730,22 +6730,22 @@
         <v>5</v>
       </c>
       <c r="AN32" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="AO32" t="n">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="AP32" t="n">
         <v>30</v>
       </c>
       <c r="AQ32" t="n">
-        <v>84.40000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="AR32" t="n">
         <v>100</v>
       </c>
       <c r="AS32" t="n">
-        <v>84.40000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>5</v>
       </c>
       <c r="AN33" t="n">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="AO33" t="n">
         <v>12</v>
@@ -6938,13 +6938,13 @@
         <v>30</v>
       </c>
       <c r="AQ33" t="n">
-        <v>43</v>
+        <v>35.8</v>
       </c>
       <c r="AR33" t="n">
         <v>100</v>
       </c>
       <c r="AS33" t="n">
-        <v>43</v>
+        <v>35.8</v>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
@@ -7128,22 +7128,22 @@
         <v>5</v>
       </c>
       <c r="AN34" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO34" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AP34" t="n">
         <v>30</v>
       </c>
       <c r="AQ34" t="n">
-        <v>53.8</v>
+        <v>47.8</v>
       </c>
       <c r="AR34" t="n">
         <v>100</v>
       </c>
       <c r="AS34" t="n">
-        <v>53.8</v>
+        <v>47.8</v>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
@@ -7330,19 +7330,19 @@
         <v>80</v>
       </c>
       <c r="AO35" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="AP35" t="n">
         <v>30</v>
       </c>
       <c r="AQ35" t="n">
-        <v>55.6</v>
+        <v>51.2</v>
       </c>
       <c r="AR35" t="n">
         <v>100</v>
       </c>
       <c r="AS35" t="n">
-        <v>55.6</v>
+        <v>51.2</v>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
@@ -7526,22 +7526,22 @@
         <v>5</v>
       </c>
       <c r="AN36" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO36" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="AP36" t="n">
         <v>30</v>
       </c>
       <c r="AQ36" t="n">
-        <v>65.40000000000001</v>
+        <v>54.2</v>
       </c>
       <c r="AR36" t="n">
         <v>100</v>
       </c>
       <c r="AS36" t="n">
-        <v>65.40000000000001</v>
+        <v>54.2</v>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
@@ -7732,19 +7732,19 @@
         <v>50</v>
       </c>
       <c r="AO37" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="AP37" t="n">
         <v>30</v>
       </c>
       <c r="AQ37" t="n">
-        <v>68.2</v>
+        <v>66.2</v>
       </c>
       <c r="AR37" t="n">
         <v>100</v>
       </c>
       <c r="AS37" t="n">
-        <v>68.2</v>
+        <v>66.2</v>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
@@ -8130,19 +8130,19 @@
         <v>80</v>
       </c>
       <c r="AO39" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="AP39" t="n">
         <v>30</v>
       </c>
       <c r="AQ39" t="n">
-        <v>57.2</v>
+        <v>51.2</v>
       </c>
       <c r="AR39" t="n">
         <v>100</v>
       </c>
       <c r="AS39" t="n">
-        <v>57.2</v>
+        <v>51.2</v>
       </c>
       <c r="AT39" t="inlineStr">
         <is>
@@ -8317,19 +8317,19 @@
         <v>90</v>
       </c>
       <c r="AO40" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AP40" t="n">
         <v>30</v>
       </c>
       <c r="AQ40" t="n">
-        <v>51.4</v>
+        <v>47.8</v>
       </c>
       <c r="AR40" t="n">
         <v>100</v>
       </c>
       <c r="AS40" t="n">
-        <v>51.4</v>
+        <v>47.8</v>
       </c>
       <c r="AT40" t="inlineStr">
         <is>
@@ -8512,19 +8512,19 @@
         <v>80</v>
       </c>
       <c r="AO41" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AP41" t="n">
         <v>30</v>
       </c>
       <c r="AQ41" t="n">
-        <v>80</v>
+        <v>75.2</v>
       </c>
       <c r="AR41" t="n">
         <v>100</v>
       </c>
       <c r="AS41" t="n">
-        <v>80</v>
+        <v>75.2</v>
       </c>
       <c r="AT41" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>5</v>
       </c>
       <c r="AM42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AN42" t="n">
         <v>80</v>
@@ -8697,13 +8697,13 @@
         <v>30</v>
       </c>
       <c r="AQ42" t="n">
-        <v>41.8</v>
+        <v>44.8</v>
       </c>
       <c r="AR42" t="n">
         <v>100</v>
       </c>
       <c r="AS42" t="n">
-        <v>41.8</v>
+        <v>44.8</v>
       </c>
       <c r="AT42" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>5</v>
       </c>
       <c r="AN43" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="AO43" t="n">
         <v>88</v>
@@ -8896,13 +8896,13 @@
         <v>30</v>
       </c>
       <c r="AQ43" t="n">
-        <v>68.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="AR43" t="n">
         <v>100</v>
       </c>
       <c r="AS43" t="n">
-        <v>68.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="AT43" t="inlineStr">
         <is>
@@ -9070,22 +9070,22 @@
         <v>5</v>
       </c>
       <c r="AN44" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="AO44" t="n">
         <v>12</v>
       </c>
       <c r="AP44" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AQ44" t="n">
-        <v>22.3</v>
+        <v>34.2</v>
       </c>
       <c r="AR44" t="n">
         <v>100</v>
       </c>
       <c r="AS44" t="n">
-        <v>22.3</v>
+        <v>34.2</v>
       </c>
       <c r="AT44" t="inlineStr">
         <is>
@@ -9269,22 +9269,22 @@
         <v>5</v>
       </c>
       <c r="AN45" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO45" t="n">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="AP45" t="n">
         <v>30</v>
       </c>
       <c r="AQ45" t="n">
-        <v>76.59999999999999</v>
+        <v>61</v>
       </c>
       <c r="AR45" t="n">
         <v>100</v>
       </c>
       <c r="AS45" t="n">
-        <v>76.59999999999999</v>
+        <v>61</v>
       </c>
       <c r="AT45" t="inlineStr">
         <is>
@@ -9667,22 +9667,22 @@
         <v>5</v>
       </c>
       <c r="AN47" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="AO47" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="AP47" t="n">
         <v>30</v>
       </c>
       <c r="AQ47" t="n">
-        <v>60.4</v>
+        <v>51.2</v>
       </c>
       <c r="AR47" t="n">
         <v>100</v>
       </c>
       <c r="AS47" t="n">
-        <v>60.4</v>
+        <v>51.2</v>
       </c>
       <c r="AT47" t="inlineStr">
         <is>
@@ -10064,19 +10064,19 @@
         <v>90</v>
       </c>
       <c r="AO49" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="AP49" t="n">
         <v>30</v>
       </c>
       <c r="AQ49" t="n">
-        <v>69</v>
+        <v>54.2</v>
       </c>
       <c r="AR49" t="n">
         <v>100</v>
       </c>
       <c r="AS49" t="n">
-        <v>69</v>
+        <v>54.2</v>
       </c>
       <c r="AT49" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         <v>5</v>
       </c>
       <c r="AN50" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AO50" t="n">
         <v>12</v>
@@ -10273,13 +10273,13 @@
         <v>30</v>
       </c>
       <c r="AQ50" t="n">
-        <v>47.2</v>
+        <v>44.8</v>
       </c>
       <c r="AR50" t="n">
         <v>100</v>
       </c>
       <c r="AS50" t="n">
-        <v>47.2</v>
+        <v>44.8</v>
       </c>
       <c r="AT50" t="inlineStr">
         <is>
@@ -10463,22 +10463,22 @@
         <v>5</v>
       </c>
       <c r="AN51" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO51" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="AP51" t="n">
         <v>30</v>
       </c>
       <c r="AQ51" t="n">
-        <v>83.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="AR51" t="n">
         <v>100</v>
       </c>
       <c r="AS51" t="n">
-        <v>83.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="AT51" t="inlineStr">
         <is>
@@ -10861,22 +10861,22 @@
         <v>5</v>
       </c>
       <c r="AN53" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO53" t="n">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="AP53" t="n">
         <v>30</v>
       </c>
       <c r="AQ53" t="n">
-        <v>79.40000000000001</v>
+        <v>61</v>
       </c>
       <c r="AR53" t="n">
         <v>100</v>
       </c>
       <c r="AS53" t="n">
-        <v>79.40000000000001</v>
+        <v>61</v>
       </c>
       <c r="AT53" t="inlineStr">
         <is>
@@ -11059,19 +11059,19 @@
         <v>90</v>
       </c>
       <c r="AO54" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="AP54" t="n">
         <v>30</v>
       </c>
       <c r="AQ54" t="n">
-        <v>67</v>
+        <v>54.2</v>
       </c>
       <c r="AR54" t="n">
         <v>100</v>
       </c>
       <c r="AS54" t="n">
-        <v>67</v>
+        <v>54.2</v>
       </c>
       <c r="AT54" t="inlineStr">
         <is>
@@ -11255,22 +11255,22 @@
         <v>5</v>
       </c>
       <c r="AN55" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO55" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AP55" t="n">
         <v>30</v>
       </c>
       <c r="AQ55" t="n">
-        <v>85.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="AR55" t="n">
         <v>100</v>
       </c>
       <c r="AS55" t="n">
-        <v>85.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="AT55" t="inlineStr">
         <is>
@@ -11454,22 +11454,22 @@
         <v>5</v>
       </c>
       <c r="AN56" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO56" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="AP56" t="n">
         <v>30</v>
       </c>
       <c r="AQ56" t="n">
-        <v>66.8</v>
+        <v>54.2</v>
       </c>
       <c r="AR56" t="n">
         <v>100</v>
       </c>
       <c r="AS56" t="n">
-        <v>66.8</v>
+        <v>54.2</v>
       </c>
       <c r="AT56" t="inlineStr">
         <is>
@@ -11656,19 +11656,19 @@
         <v>90</v>
       </c>
       <c r="AO57" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="AP57" t="n">
         <v>30</v>
       </c>
       <c r="AQ57" t="n">
-        <v>60.2</v>
+        <v>47.8</v>
       </c>
       <c r="AR57" t="n">
         <v>100</v>
       </c>
       <c r="AS57" t="n">
-        <v>60.2</v>
+        <v>47.8</v>
       </c>
       <c r="AT57" t="inlineStr">
         <is>
@@ -11859,19 +11859,19 @@
         <v>90</v>
       </c>
       <c r="AO58" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="AP58" t="n">
         <v>30</v>
       </c>
       <c r="AQ58" t="n">
-        <v>81.8</v>
+        <v>78.2</v>
       </c>
       <c r="AR58" t="n">
         <v>100</v>
       </c>
       <c r="AS58" t="n">
-        <v>81.8</v>
+        <v>78.2</v>
       </c>
       <c r="AT58" t="inlineStr">
         <is>
@@ -12054,19 +12054,19 @@
         <v>90</v>
       </c>
       <c r="AO59" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="AP59" t="n">
         <v>30</v>
       </c>
       <c r="AQ59" t="n">
-        <v>56.2</v>
+        <v>54.2</v>
       </c>
       <c r="AR59" t="n">
         <v>100</v>
       </c>
       <c r="AS59" t="n">
-        <v>56.2</v>
+        <v>54.2</v>
       </c>
       <c r="AT59" t="inlineStr">
         <is>
@@ -12253,19 +12253,19 @@
         <v>90</v>
       </c>
       <c r="AO60" t="n">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="AP60" t="n">
         <v>30</v>
       </c>
       <c r="AQ60" t="n">
-        <v>74.2</v>
+        <v>61</v>
       </c>
       <c r="AR60" t="n">
         <v>100</v>
       </c>
       <c r="AS60" t="n">
-        <v>74.2</v>
+        <v>61</v>
       </c>
       <c r="AT60" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>5</v>
       </c>
       <c r="AN61" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AO61" t="n">
         <v>76</v>
@@ -12458,13 +12458,13 @@
         <v>30</v>
       </c>
       <c r="AQ61" t="n">
-        <v>72.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AR61" t="n">
         <v>100</v>
       </c>
       <c r="AS61" t="n">
-        <v>72.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AT61" t="inlineStr">
         <is>
@@ -12640,22 +12640,22 @@
         <v>5</v>
       </c>
       <c r="AN62" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO62" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="AP62" t="n">
         <v>30</v>
       </c>
       <c r="AQ62" t="n">
-        <v>60.2</v>
+        <v>54.2</v>
       </c>
       <c r="AR62" t="n">
         <v>100</v>
       </c>
       <c r="AS62" t="n">
-        <v>60.2</v>
+        <v>54.2</v>
       </c>
       <c r="AT62" t="inlineStr">
         <is>
@@ -12839,22 +12839,22 @@
         <v>5</v>
       </c>
       <c r="AN63" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AO63" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="AP63" t="n">
         <v>30</v>
       </c>
       <c r="AQ63" t="n">
-        <v>74.40000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="AR63" t="n">
         <v>100</v>
       </c>
       <c r="AS63" t="n">
-        <v>74.40000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="AT63" t="inlineStr">
         <is>
@@ -13038,22 +13038,22 @@
         <v>5</v>
       </c>
       <c r="AN64" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AO64" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AP64" t="n">
         <v>30</v>
       </c>
       <c r="AQ64" t="n">
-        <v>58.4</v>
+        <v>51.2</v>
       </c>
       <c r="AR64" t="n">
         <v>100</v>
       </c>
       <c r="AS64" t="n">
-        <v>58.4</v>
+        <v>51.2</v>
       </c>
       <c r="AT64" t="inlineStr">
         <is>
@@ -13237,22 +13237,22 @@
         <v>5</v>
       </c>
       <c r="AN65" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO65" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AP65" t="n">
         <v>30</v>
       </c>
       <c r="AQ65" t="n">
-        <v>85.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="AR65" t="n">
         <v>100</v>
       </c>
       <c r="AS65" t="n">
-        <v>85.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="AT65" t="inlineStr">
         <is>
@@ -13439,19 +13439,19 @@
         <v>90</v>
       </c>
       <c r="AO66" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AP66" t="n">
         <v>30</v>
       </c>
       <c r="AQ66" t="n">
-        <v>83</v>
+        <v>78.2</v>
       </c>
       <c r="AR66" t="n">
         <v>100</v>
       </c>
       <c r="AS66" t="n">
-        <v>83</v>
+        <v>78.2</v>
       </c>
       <c r="AT66" t="inlineStr">
         <is>
@@ -13638,19 +13638,19 @@
         <v>80</v>
       </c>
       <c r="AO67" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="AP67" t="n">
         <v>30</v>
       </c>
       <c r="AQ67" t="n">
-        <v>58.4</v>
+        <v>51.2</v>
       </c>
       <c r="AR67" t="n">
         <v>100</v>
       </c>
       <c r="AS67" t="n">
-        <v>58.4</v>
+        <v>51.2</v>
       </c>
       <c r="AT67" t="inlineStr">
         <is>
@@ -14036,19 +14036,19 @@
         <v>50</v>
       </c>
       <c r="AO69" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AP69" t="n">
         <v>30</v>
       </c>
       <c r="AQ69" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="AR69" t="n">
         <v>100</v>
       </c>
       <c r="AS69" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="AT69" t="inlineStr">
         <is>
@@ -14232,22 +14232,22 @@
         <v>5</v>
       </c>
       <c r="AN70" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO70" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AP70" t="n">
         <v>30</v>
       </c>
       <c r="AQ70" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="AR70" t="n">
         <v>100</v>
       </c>
       <c r="AS70" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="AT70" t="inlineStr">
         <is>
@@ -14427,22 +14427,22 @@
         <v>5</v>
       </c>
       <c r="AN71" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO71" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="AP71" t="n">
         <v>30</v>
       </c>
       <c r="AQ71" t="n">
-        <v>67.2</v>
+        <v>61</v>
       </c>
       <c r="AR71" t="n">
         <v>100</v>
       </c>
       <c r="AS71" t="n">
-        <v>67.2</v>
+        <v>61</v>
       </c>
       <c r="AT71" t="inlineStr">
         <is>
@@ -14618,22 +14618,22 @@
         <v>5</v>
       </c>
       <c r="AN72" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AO72" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AP72" t="n">
         <v>30</v>
       </c>
       <c r="AQ72" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="AR72" t="n">
         <v>100</v>
       </c>
       <c r="AS72" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="AT72" t="inlineStr">
         <is>
@@ -14816,19 +14816,19 @@
         <v>90</v>
       </c>
       <c r="AO73" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="AP73" t="n">
         <v>30</v>
       </c>
       <c r="AQ73" t="n">
-        <v>60.2</v>
+        <v>54.2</v>
       </c>
       <c r="AR73" t="n">
         <v>100</v>
       </c>
       <c r="AS73" t="n">
-        <v>60.2</v>
+        <v>54.2</v>
       </c>
       <c r="AT73" t="inlineStr">
         <is>
@@ -15207,22 +15207,22 @@
         <v>5</v>
       </c>
       <c r="AN75" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO75" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="AP75" t="n">
         <v>30</v>
       </c>
       <c r="AQ75" t="n">
-        <v>64.59999999999999</v>
+        <v>54.2</v>
       </c>
       <c r="AR75" t="n">
         <v>100</v>
       </c>
       <c r="AS75" t="n">
-        <v>64.59999999999999</v>
+        <v>54.2</v>
       </c>
       <c r="AT75" t="inlineStr">
         <is>
@@ -15406,22 +15406,22 @@
         <v>5</v>
       </c>
       <c r="AN76" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO76" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="AP76" t="n">
         <v>30</v>
       </c>
       <c r="AQ76" t="n">
-        <v>84.8</v>
+        <v>78.2</v>
       </c>
       <c r="AR76" t="n">
         <v>100</v>
       </c>
       <c r="AS76" t="n">
-        <v>84.8</v>
+        <v>78.2</v>
       </c>
       <c r="AT76" t="inlineStr">
         <is>
@@ -15605,22 +15605,22 @@
         <v>5</v>
       </c>
       <c r="AN77" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO77" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AP77" t="n">
         <v>30</v>
       </c>
       <c r="AQ77" t="n">
-        <v>54</v>
+        <v>47.8</v>
       </c>
       <c r="AR77" t="n">
         <v>100</v>
       </c>
       <c r="AS77" t="n">
-        <v>54</v>
+        <v>47.8</v>
       </c>
       <c r="AT77" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>5</v>
       </c>
       <c r="AN78" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO78" t="n">
         <v>28</v>
@@ -15813,13 +15813,13 @@
         <v>30</v>
       </c>
       <c r="AQ78" t="n">
-        <v>56.6</v>
+        <v>54.2</v>
       </c>
       <c r="AR78" t="n">
         <v>100</v>
       </c>
       <c r="AS78" t="n">
-        <v>56.6</v>
+        <v>54.2</v>
       </c>
       <c r="AT78" t="inlineStr">
         <is>
@@ -16003,22 +16003,22 @@
         <v>5</v>
       </c>
       <c r="AN79" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AO79" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="AP79" t="n">
         <v>30</v>
       </c>
       <c r="AQ79" t="n">
-        <v>67.59999999999999</v>
+        <v>58</v>
       </c>
       <c r="AR79" t="n">
         <v>100</v>
       </c>
       <c r="AS79" t="n">
-        <v>67.59999999999999</v>
+        <v>58</v>
       </c>
       <c r="AT79" t="inlineStr">
         <is>
@@ -16206,22 +16206,22 @@
         <v>5</v>
       </c>
       <c r="AN80" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO80" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="AP80" t="n">
         <v>30</v>
       </c>
       <c r="AQ80" t="n">
-        <v>85.2</v>
+        <v>78.2</v>
       </c>
       <c r="AR80" t="n">
         <v>100</v>
       </c>
       <c r="AS80" t="n">
-        <v>85.2</v>
+        <v>78.2</v>
       </c>
       <c r="AT80" t="inlineStr">
         <is>
@@ -16409,22 +16409,22 @@
         <v>5</v>
       </c>
       <c r="AN81" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO81" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="AP81" t="n">
         <v>30</v>
       </c>
       <c r="AQ81" t="n">
-        <v>69.59999999999999</v>
+        <v>61</v>
       </c>
       <c r="AR81" t="n">
         <v>100</v>
       </c>
       <c r="AS81" t="n">
-        <v>69.59999999999999</v>
+        <v>61</v>
       </c>
       <c r="AT81" t="inlineStr">
         <is>
@@ -16608,22 +16608,22 @@
         <v>5</v>
       </c>
       <c r="AN82" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO82" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AP82" t="n">
         <v>30</v>
       </c>
       <c r="AQ82" t="n">
-        <v>85.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="AR82" t="n">
         <v>100</v>
       </c>
       <c r="AS82" t="n">
-        <v>85.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="AT82" t="inlineStr">
         <is>
@@ -16810,19 +16810,19 @@
         <v>50</v>
       </c>
       <c r="AO83" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="AP83" t="n">
         <v>30</v>
       </c>
       <c r="AQ83" t="n">
-        <v>53.8</v>
+        <v>49</v>
       </c>
       <c r="AR83" t="n">
         <v>100</v>
       </c>
       <c r="AS83" t="n">
-        <v>53.8</v>
+        <v>49</v>
       </c>
       <c r="AT83" t="inlineStr">
         <is>
@@ -17006,22 +17006,22 @@
         <v>5</v>
       </c>
       <c r="AN84" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="AO84" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AP84" t="n">
         <v>30</v>
       </c>
       <c r="AQ84" t="n">
-        <v>77.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AR84" t="n">
         <v>100</v>
       </c>
       <c r="AS84" t="n">
-        <v>77.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AT84" t="inlineStr">
         <is>
@@ -17205,22 +17205,22 @@
         <v>5</v>
       </c>
       <c r="AN85" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO85" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="AP85" t="n">
         <v>30</v>
       </c>
       <c r="AQ85" t="n">
-        <v>84.8</v>
+        <v>78.2</v>
       </c>
       <c r="AR85" t="n">
         <v>100</v>
       </c>
       <c r="AS85" t="n">
-        <v>84.8</v>
+        <v>78.2</v>
       </c>
       <c r="AT85" t="inlineStr">
         <is>
@@ -17407,19 +17407,19 @@
         <v>80</v>
       </c>
       <c r="AO86" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="AP86" t="n">
         <v>30</v>
       </c>
       <c r="AQ86" t="n">
-        <v>60.8</v>
+        <v>58</v>
       </c>
       <c r="AR86" t="n">
         <v>100</v>
       </c>
       <c r="AS86" t="n">
-        <v>60.8</v>
+        <v>58</v>
       </c>
       <c r="AT86" t="inlineStr">
         <is>
@@ -17606,19 +17606,19 @@
         <v>80</v>
       </c>
       <c r="AO87" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AP87" t="n">
         <v>30</v>
       </c>
       <c r="AQ87" t="n">
-        <v>48.4</v>
+        <v>44.8</v>
       </c>
       <c r="AR87" t="n">
         <v>100</v>
       </c>
       <c r="AS87" t="n">
-        <v>48.4</v>
+        <v>44.8</v>
       </c>
       <c r="AT87" t="inlineStr">
         <is>
@@ -17798,22 +17798,22 @@
         <v>5</v>
       </c>
       <c r="AN88" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO88" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="AP88" t="n">
         <v>30</v>
       </c>
       <c r="AQ88" t="n">
-        <v>85.2</v>
+        <v>78.2</v>
       </c>
       <c r="AR88" t="n">
         <v>100</v>
       </c>
       <c r="AS88" t="n">
-        <v>85.2</v>
+        <v>78.2</v>
       </c>
       <c r="AT88" t="inlineStr">
         <is>
@@ -17996,19 +17996,19 @@
         <v>80</v>
       </c>
       <c r="AO89" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AP89" t="n">
         <v>30</v>
       </c>
       <c r="AQ89" t="n">
-        <v>48.4</v>
+        <v>44.8</v>
       </c>
       <c r="AR89" t="n">
         <v>100</v>
       </c>
       <c r="AS89" t="n">
-        <v>48.4</v>
+        <v>44.8</v>
       </c>
       <c r="AT89" t="inlineStr">
         <is>
@@ -18192,22 +18192,22 @@
         <v>5</v>
       </c>
       <c r="AN90" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="AO90" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="AP90" t="n">
         <v>30</v>
       </c>
       <c r="AQ90" t="n">
-        <v>73.40000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="AR90" t="n">
         <v>100</v>
       </c>
       <c r="AS90" t="n">
-        <v>73.40000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="AT90" t="inlineStr">
         <is>
@@ -18391,22 +18391,22 @@
         <v>5</v>
       </c>
       <c r="AN91" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO91" t="n">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="AP91" t="n">
         <v>30</v>
       </c>
       <c r="AQ91" t="n">
-        <v>83.2</v>
+        <v>67.8</v>
       </c>
       <c r="AR91" t="n">
         <v>100</v>
       </c>
       <c r="AS91" t="n">
-        <v>83.2</v>
+        <v>67.8</v>
       </c>
       <c r="AT91" t="inlineStr">
         <is>
@@ -18586,22 +18586,22 @@
         <v>5</v>
       </c>
       <c r="AN92" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO92" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="AP92" t="n">
         <v>30</v>
       </c>
       <c r="AQ92" t="n">
-        <v>86</v>
+        <v>67.8</v>
       </c>
       <c r="AR92" t="n">
         <v>100</v>
       </c>
       <c r="AS92" t="n">
-        <v>86</v>
+        <v>67.8</v>
       </c>
       <c r="AT92" t="inlineStr">
         <is>
@@ -18781,22 +18781,22 @@
         <v>5</v>
       </c>
       <c r="AN93" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO93" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AP93" t="n">
         <v>30</v>
       </c>
       <c r="AQ93" t="n">
-        <v>85.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AR93" t="n">
         <v>100</v>
       </c>
       <c r="AS93" t="n">
-        <v>85.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AT93" t="inlineStr">
         <is>
@@ -18980,22 +18980,22 @@
         <v>5</v>
       </c>
       <c r="AN94" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AO94" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="AP94" t="n">
         <v>30</v>
       </c>
       <c r="AQ94" t="n">
-        <v>67.2</v>
+        <v>51.2</v>
       </c>
       <c r="AR94" t="n">
         <v>100</v>
       </c>
       <c r="AS94" t="n">
-        <v>67.2</v>
+        <v>51.2</v>
       </c>
       <c r="AT94" t="inlineStr">
         <is>
@@ -19179,22 +19179,22 @@
         <v>5</v>
       </c>
       <c r="AN95" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AO95" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="AP95" t="n">
         <v>30</v>
       </c>
       <c r="AQ95" t="n">
-        <v>58.4</v>
+        <v>44.8</v>
       </c>
       <c r="AR95" t="n">
         <v>100</v>
       </c>
       <c r="AS95" t="n">
-        <v>58.4</v>
+        <v>44.8</v>
       </c>
       <c r="AT95" t="inlineStr">
         <is>
@@ -19377,19 +19377,19 @@
         <v>90</v>
       </c>
       <c r="AO96" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AP96" t="n">
         <v>30</v>
       </c>
       <c r="AQ96" t="n">
-        <v>56.6</v>
+        <v>54.2</v>
       </c>
       <c r="AR96" t="n">
         <v>100</v>
       </c>
       <c r="AS96" t="n">
-        <v>56.6</v>
+        <v>54.2</v>
       </c>
       <c r="AT96" t="inlineStr">
         <is>
@@ -19573,22 +19573,22 @@
         <v>5</v>
       </c>
       <c r="AN97" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO97" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AP97" t="n">
         <v>30</v>
       </c>
       <c r="AQ97" t="n">
-        <v>86</v>
+        <v>78.2</v>
       </c>
       <c r="AR97" t="n">
         <v>100</v>
       </c>
       <c r="AS97" t="n">
-        <v>86</v>
+        <v>78.2</v>
       </c>
       <c r="AT97" t="inlineStr">
         <is>
@@ -19779,19 +19779,19 @@
         <v>80</v>
       </c>
       <c r="AO98" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AP98" t="n">
         <v>30</v>
       </c>
       <c r="AQ98" t="n">
-        <v>55.2</v>
+        <v>51.2</v>
       </c>
       <c r="AR98" t="n">
         <v>100</v>
       </c>
       <c r="AS98" t="n">
-        <v>55.2</v>
+        <v>51.2</v>
       </c>
       <c r="AT98" t="inlineStr">
         <is>
@@ -19975,22 +19975,22 @@
         <v>5</v>
       </c>
       <c r="AN99" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO99" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="AP99" t="n">
         <v>30</v>
       </c>
       <c r="AQ99" t="n">
-        <v>67.59999999999999</v>
+        <v>61</v>
       </c>
       <c r="AR99" t="n">
         <v>100</v>
       </c>
       <c r="AS99" t="n">
-        <v>67.59999999999999</v>
+        <v>61</v>
       </c>
       <c r="AT99" t="inlineStr">
         <is>
@@ -20177,19 +20177,19 @@
         <v>50</v>
       </c>
       <c r="AO100" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AP100" t="n">
         <v>30</v>
       </c>
       <c r="AQ100" t="n">
-        <v>44.6</v>
+        <v>42.2</v>
       </c>
       <c r="AR100" t="n">
         <v>100</v>
       </c>
       <c r="AS100" t="n">
-        <v>44.6</v>
+        <v>42.2</v>
       </c>
       <c r="AT100" t="inlineStr">
         <is>
@@ -20376,19 +20376,19 @@
         <v>90</v>
       </c>
       <c r="AO101" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AP101" t="n">
         <v>30</v>
       </c>
       <c r="AQ101" t="n">
-        <v>51.4</v>
+        <v>47.8</v>
       </c>
       <c r="AR101" t="n">
         <v>100</v>
       </c>
       <c r="AS101" t="n">
-        <v>51.4</v>
+        <v>47.8</v>
       </c>
       <c r="AT101" t="inlineStr">
         <is>
@@ -20575,19 +20575,19 @@
         <v>80</v>
       </c>
       <c r="AO102" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AP102" t="n">
         <v>30</v>
       </c>
       <c r="AQ102" t="n">
-        <v>80</v>
+        <v>75.2</v>
       </c>
       <c r="AR102" t="n">
         <v>100</v>
       </c>
       <c r="AS102" t="n">
-        <v>80</v>
+        <v>75.2</v>
       </c>
       <c r="AT102" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>5</v>
       </c>
       <c r="AN103" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AO103" t="n">
         <v>45</v>
@@ -20776,13 +20776,13 @@
         <v>30</v>
       </c>
       <c r="AQ103" t="n">
-        <v>60.4</v>
+        <v>58</v>
       </c>
       <c r="AR103" t="n">
         <v>100</v>
       </c>
       <c r="AS103" t="n">
-        <v>60.4</v>
+        <v>58</v>
       </c>
       <c r="AT103" t="inlineStr">
         <is>
@@ -20966,22 +20966,22 @@
         <v>5</v>
       </c>
       <c r="AN104" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AO104" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="AP104" t="n">
         <v>30</v>
       </c>
       <c r="AQ104" t="n">
-        <v>58.5</v>
+        <v>51.2</v>
       </c>
       <c r="AR104" t="n">
         <v>100</v>
       </c>
       <c r="AS104" t="n">
-        <v>58.5</v>
+        <v>51.2</v>
       </c>
       <c r="AT104" t="inlineStr">
         <is>
@@ -21165,22 +21165,22 @@
         <v>5</v>
       </c>
       <c r="AN105" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AO105" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AP105" t="n">
         <v>30</v>
       </c>
       <c r="AQ105" t="n">
-        <v>76.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AR105" t="n">
         <v>100</v>
       </c>
       <c r="AS105" t="n">
-        <v>76.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AT105" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>5</v>
       </c>
       <c r="AN106" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO106" t="n">
         <v>28</v>
@@ -21369,13 +21369,13 @@
         <v>30</v>
       </c>
       <c r="AQ106" t="n">
-        <v>56.6</v>
+        <v>54.2</v>
       </c>
       <c r="AR106" t="n">
         <v>100</v>
       </c>
       <c r="AS106" t="n">
-        <v>56.6</v>
+        <v>54.2</v>
       </c>
       <c r="AT106" t="inlineStr">
         <is>
@@ -21559,22 +21559,22 @@
         <v>5</v>
       </c>
       <c r="AN107" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO107" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AP107" t="n">
         <v>30</v>
       </c>
       <c r="AQ107" t="n">
-        <v>67.40000000000001</v>
+        <v>61</v>
       </c>
       <c r="AR107" t="n">
         <v>100</v>
       </c>
       <c r="AS107" t="n">
-        <v>67.40000000000001</v>
+        <v>61</v>
       </c>
       <c r="AT107" t="inlineStr">
         <is>
@@ -21758,22 +21758,22 @@
         <v>5</v>
       </c>
       <c r="AN108" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="AO108" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="AP108" t="n">
         <v>30</v>
       </c>
       <c r="AQ108" t="n">
-        <v>50.6</v>
+        <v>42.2</v>
       </c>
       <c r="AR108" t="n">
         <v>100</v>
       </c>
       <c r="AS108" t="n">
-        <v>50.6</v>
+        <v>42.2</v>
       </c>
       <c r="AT108" t="inlineStr">
         <is>
@@ -21956,19 +21956,19 @@
         <v>80</v>
       </c>
       <c r="AO109" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="AP109" t="n">
         <v>30</v>
       </c>
       <c r="AQ109" t="n">
-        <v>54.8</v>
+        <v>51.2</v>
       </c>
       <c r="AR109" t="n">
         <v>100</v>
       </c>
       <c r="AS109" t="n">
-        <v>54.8</v>
+        <v>51.2</v>
       </c>
       <c r="AT109" t="inlineStr">
         <is>
@@ -22155,19 +22155,19 @@
         <v>80</v>
       </c>
       <c r="AO110" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AP110" t="n">
         <v>30</v>
       </c>
       <c r="AQ110" t="n">
-        <v>56.8</v>
+        <v>51.2</v>
       </c>
       <c r="AR110" t="n">
         <v>100</v>
       </c>
       <c r="AS110" t="n">
-        <v>56.8</v>
+        <v>51.2</v>
       </c>
       <c r="AT110" t="inlineStr">
         <is>
@@ -22351,22 +22351,22 @@
         <v>5</v>
       </c>
       <c r="AN111" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO111" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AP111" t="n">
         <v>30</v>
       </c>
       <c r="AQ111" t="n">
-        <v>86</v>
+        <v>78.2</v>
       </c>
       <c r="AR111" t="n">
         <v>100</v>
       </c>
       <c r="AS111" t="n">
-        <v>86</v>
+        <v>78.2</v>
       </c>
       <c r="AT111" t="inlineStr">
         <is>
@@ -22553,19 +22553,19 @@
         <v>90</v>
       </c>
       <c r="AO112" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AP112" t="n">
         <v>30</v>
       </c>
       <c r="AQ112" t="n">
-        <v>59.8</v>
+        <v>54.2</v>
       </c>
       <c r="AR112" t="n">
         <v>100</v>
       </c>
       <c r="AS112" t="n">
-        <v>59.8</v>
+        <v>54.2</v>
       </c>
       <c r="AT112" t="inlineStr">
         <is>
@@ -22749,22 +22749,22 @@
         <v>5</v>
       </c>
       <c r="AN113" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AO113" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AP113" t="n">
         <v>30</v>
       </c>
       <c r="AQ113" t="n">
-        <v>62.4</v>
+        <v>58</v>
       </c>
       <c r="AR113" t="n">
         <v>100</v>
       </c>
       <c r="AS113" t="n">
-        <v>62.4</v>
+        <v>58</v>
       </c>
       <c r="AT113" t="inlineStr">
         <is>
@@ -22951,19 +22951,19 @@
         <v>90</v>
       </c>
       <c r="AO114" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AP114" t="n">
         <v>30</v>
       </c>
       <c r="AQ114" t="n">
-        <v>83</v>
+        <v>78.2</v>
       </c>
       <c r="AR114" t="n">
         <v>100</v>
       </c>
       <c r="AS114" t="n">
-        <v>83</v>
+        <v>78.2</v>
       </c>
       <c r="AT114" t="inlineStr">
         <is>
@@ -23151,22 +23151,22 @@
         <v>5</v>
       </c>
       <c r="AN115" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO115" t="n">
         <v>88</v>
-      </c>
-      <c r="AO115" t="n">
-        <v>96</v>
       </c>
       <c r="AP115" t="n">
         <v>30</v>
       </c>
       <c r="AQ115" t="n">
-        <v>80.8</v>
+        <v>75.2</v>
       </c>
       <c r="AR115" t="n">
         <v>100</v>
       </c>
       <c r="AS115" t="n">
-        <v>80.8</v>
+        <v>75.2</v>
       </c>
       <c r="AT115" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>5</v>
       </c>
       <c r="AN116" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="AO116" t="n">
         <v>62</v>
@@ -23363,13 +23363,13 @@
         <v>30</v>
       </c>
       <c r="AQ116" t="n">
-        <v>60.6</v>
+        <v>55.8</v>
       </c>
       <c r="AR116" t="n">
         <v>100</v>
       </c>
       <c r="AS116" t="n">
-        <v>60.6</v>
+        <v>55.8</v>
       </c>
       <c r="AT116" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
         <v>5</v>
       </c>
       <c r="AN117" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="AO117" t="n">
         <v>88</v>
@@ -23562,13 +23562,13 @@
         <v>30</v>
       </c>
       <c r="AQ117" t="n">
-        <v>68.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="AR117" t="n">
         <v>100</v>
       </c>
       <c r="AS117" t="n">
-        <v>68.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="AT117" t="inlineStr">
         <is>
@@ -23752,22 +23752,22 @@
         <v>5</v>
       </c>
       <c r="AN118" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO118" t="n">
         <v>88</v>
-      </c>
-      <c r="AO118" t="n">
-        <v>100</v>
       </c>
       <c r="AP118" t="n">
         <v>30</v>
       </c>
       <c r="AQ118" t="n">
-        <v>82.40000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="AR118" t="n">
         <v>100</v>
       </c>
       <c r="AS118" t="n">
-        <v>82.40000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="AT118" t="inlineStr">
         <is>
@@ -23954,19 +23954,19 @@
         <v>80</v>
       </c>
       <c r="AO119" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AP119" t="n">
         <v>30</v>
       </c>
       <c r="AQ119" t="n">
-        <v>73.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AR119" t="n">
         <v>100</v>
       </c>
       <c r="AS119" t="n">
-        <v>73.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AT119" t="inlineStr">
         <is>
@@ -24153,19 +24153,19 @@
         <v>90</v>
       </c>
       <c r="AO120" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP120" t="n">
         <v>30</v>
       </c>
       <c r="AQ120" t="n">
-        <v>47.4</v>
+        <v>47.8</v>
       </c>
       <c r="AR120" t="n">
         <v>100</v>
       </c>
       <c r="AS120" t="n">
-        <v>47.4</v>
+        <v>47.8</v>
       </c>
       <c r="AT120" t="inlineStr">
         <is>
